--- a/DESCARGAR DOCUMENTACIÓN/Documentos_ingeniería/Cronograma General del Proyecto.xlsx
+++ b/DESCARGAR DOCUMENTACIÓN/Documentos_ingeniería/Cronograma General del Proyecto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sedima0.sharepoint.com/sites/SharePoint/Documentos compartidos/Archivos Tecnicos/3. Proyectos/DEMO GLV/Editables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="13_ncr:1_{6CACEEBB-D3AA-4075-B106-05FD742C5C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C9A70F1-4ECE-4B2B-9CB2-76ECAD257930}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{6CACEEBB-D3AA-4075-B106-05FD742C5C86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57064FB3-D780-454A-8039-CF91B0547C16}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8E8D3080-CF53-455E-A891-8DF80FB9339E}"/>
   </bookViews>
@@ -892,9 +892,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="3" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -914,6 +911,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -943,8 +943,8 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -958,9 +958,6 @@
     <xf numFmtId="9" fontId="0" fillId="2" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -970,8 +967,11 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -979,19 +979,19 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -999,9 +999,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1015,12 +1012,6 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1030,19 +1021,25 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1078,14 +1075,17 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3313,52 +3313,8 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>80910</xdr:colOff>
-      <xdr:row>109</xdr:row>
-      <xdr:rowOff>70203</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>277090</xdr:colOff>
-      <xdr:row>121</xdr:row>
-      <xdr:rowOff>886691</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Imagen 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C1AA5BB-84A8-36B7-64D5-BF80294FA86D}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="468837" y="18884676"/>
-          <a:ext cx="10947308" cy="7993141"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>249381</xdr:colOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
       <xdr:row>110</xdr:row>
       <xdr:rowOff>13854</xdr:rowOff>
     </xdr:from>
@@ -3382,6 +3338,50 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12134850" y="19482954"/>
+          <a:ext cx="7852596" cy="7959436"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>110</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>121</xdr:row>
+      <xdr:rowOff>914401</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CA77974-8FE1-A4CA-96A7-9C329A61C75D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
@@ -3389,8 +3389,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11388436" y="19008436"/>
-          <a:ext cx="8936715" cy="7869381"/>
+          <a:off x="438150" y="19507201"/>
+          <a:ext cx="11658600" cy="7962900"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3400,6 +3400,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3740,7 +3744,7 @@
     <col min="34" max="34" width="9.44140625" customWidth="1"/>
     <col min="35" max="35" width="10.44140625" customWidth="1"/>
     <col min="36" max="36" width="4" customWidth="1"/>
-    <col min="37" max="37" width="2.88671875" customWidth="1"/>
+    <col min="37" max="37" width="9" customWidth="1"/>
     <col min="38" max="39" width="6.77734375" customWidth="1"/>
     <col min="40" max="40" width="18.21875" customWidth="1"/>
     <col min="41" max="42" width="10.77734375" customWidth="1"/>
@@ -3899,39 +3903,39 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="118" t="s">
+      <c r="G3" s="115" t="s">
         <v>80</v>
       </c>
-      <c r="H3" s="118"/>
-      <c r="I3" s="118"/>
-      <c r="J3" s="118"/>
-      <c r="K3" s="118"/>
-      <c r="L3" s="118"/>
-      <c r="M3" s="118"/>
-      <c r="N3" s="118"/>
-      <c r="O3" s="118"/>
-      <c r="P3" s="118"/>
-      <c r="Q3" s="118"/>
-      <c r="R3" s="118"/>
-      <c r="S3" s="118"/>
-      <c r="T3" s="118"/>
-      <c r="U3" s="118"/>
-      <c r="V3" s="118"/>
-      <c r="W3" s="118"/>
-      <c r="X3" s="118"/>
-      <c r="Y3" s="118"/>
-      <c r="Z3" s="118"/>
-      <c r="AA3" s="118"/>
-      <c r="AB3" s="118"/>
-      <c r="AC3" s="118"/>
-      <c r="AD3" s="118"/>
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="K3" s="115"/>
+      <c r="L3" s="115"/>
+      <c r="M3" s="115"/>
+      <c r="N3" s="115"/>
+      <c r="O3" s="115"/>
+      <c r="P3" s="115"/>
+      <c r="Q3" s="115"/>
+      <c r="R3" s="115"/>
+      <c r="S3" s="115"/>
+      <c r="T3" s="115"/>
+      <c r="U3" s="115"/>
+      <c r="V3" s="115"/>
+      <c r="W3" s="115"/>
+      <c r="X3" s="115"/>
+      <c r="Y3" s="115"/>
+      <c r="Z3" s="115"/>
+      <c r="AA3" s="115"/>
+      <c r="AB3" s="115"/>
+      <c r="AC3" s="115"/>
+      <c r="AD3" s="115"/>
       <c r="AE3" s="52"/>
-      <c r="AF3" s="54" t="s">
+      <c r="AF3" s="116" t="s">
         <v>79</v>
       </c>
-      <c r="AG3" s="54"/>
-      <c r="AH3" s="54"/>
-      <c r="AI3" s="54"/>
+      <c r="AG3" s="116"/>
+      <c r="AH3" s="116"/>
+      <c r="AI3" s="116"/>
       <c r="AJ3" s="6"/>
       <c r="AK3" s="1"/>
       <c r="AL3" s="1"/>
@@ -3971,37 +3975,37 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="118"/>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118"/>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118"/>
-      <c r="L4" s="118"/>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118"/>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118"/>
-      <c r="V4" s="118"/>
-      <c r="W4" s="118"/>
-      <c r="X4" s="118"/>
-      <c r="Y4" s="118"/>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="118"/>
+      <c r="G4" s="115"/>
+      <c r="H4" s="115"/>
+      <c r="I4" s="115"/>
+      <c r="J4" s="115"/>
+      <c r="K4" s="115"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
+      <c r="N4" s="115"/>
+      <c r="O4" s="115"/>
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="115"/>
+      <c r="U4" s="115"/>
+      <c r="V4" s="115"/>
+      <c r="W4" s="115"/>
+      <c r="X4" s="115"/>
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
+      <c r="AA4" s="115"/>
+      <c r="AB4" s="115"/>
+      <c r="AC4" s="115"/>
+      <c r="AD4" s="115"/>
       <c r="AE4" s="52"/>
-      <c r="AF4" s="54" t="s">
+      <c r="AF4" s="116" t="s">
         <v>78</v>
       </c>
-      <c r="AG4" s="54"/>
-      <c r="AH4" s="54"/>
-      <c r="AI4" s="54"/>
+      <c r="AG4" s="116"/>
+      <c r="AH4" s="116"/>
+      <c r="AI4" s="116"/>
       <c r="AJ4" s="6"/>
       <c r="AK4" s="1"/>
       <c r="AL4" s="1"/>
@@ -4041,37 +4045,37 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
-      <c r="O5" s="118"/>
-      <c r="P5" s="118"/>
-      <c r="Q5" s="118"/>
-      <c r="R5" s="118"/>
-      <c r="S5" s="118"/>
-      <c r="T5" s="118"/>
-      <c r="U5" s="118"/>
-      <c r="V5" s="118"/>
-      <c r="W5" s="118"/>
-      <c r="X5" s="118"/>
-      <c r="Y5" s="118"/>
-      <c r="Z5" s="118"/>
-      <c r="AA5" s="118"/>
-      <c r="AB5" s="118"/>
-      <c r="AC5" s="118"/>
-      <c r="AD5" s="118"/>
+      <c r="G5" s="115"/>
+      <c r="H5" s="115"/>
+      <c r="I5" s="115"/>
+      <c r="J5" s="115"/>
+      <c r="K5" s="115"/>
+      <c r="L5" s="115"/>
+      <c r="M5" s="115"/>
+      <c r="N5" s="115"/>
+      <c r="O5" s="115"/>
+      <c r="P5" s="115"/>
+      <c r="Q5" s="115"/>
+      <c r="R5" s="115"/>
+      <c r="S5" s="115"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="115"/>
+      <c r="V5" s="115"/>
+      <c r="W5" s="115"/>
+      <c r="X5" s="115"/>
+      <c r="Y5" s="115"/>
+      <c r="Z5" s="115"/>
+      <c r="AA5" s="115"/>
+      <c r="AB5" s="115"/>
+      <c r="AC5" s="115"/>
+      <c r="AD5" s="115"/>
       <c r="AE5" s="52"/>
-      <c r="AF5" s="54" t="s">
+      <c r="AF5" s="116" t="s">
         <v>77</v>
       </c>
-      <c r="AG5" s="54"/>
-      <c r="AH5" s="54"/>
-      <c r="AI5" s="54"/>
+      <c r="AG5" s="116"/>
+      <c r="AH5" s="116"/>
+      <c r="AI5" s="116"/>
       <c r="AJ5" s="6"/>
       <c r="AK5" s="1"/>
       <c r="AL5" s="1"/>
@@ -4111,37 +4115,37 @@
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="G6" s="118"/>
-      <c r="H6" s="118"/>
-      <c r="I6" s="118"/>
-      <c r="J6" s="118"/>
-      <c r="K6" s="118"/>
-      <c r="L6" s="118"/>
-      <c r="M6" s="118"/>
-      <c r="N6" s="118"/>
-      <c r="O6" s="118"/>
-      <c r="P6" s="118"/>
-      <c r="Q6" s="118"/>
-      <c r="R6" s="118"/>
-      <c r="S6" s="118"/>
-      <c r="T6" s="118"/>
-      <c r="U6" s="118"/>
-      <c r="V6" s="118"/>
-      <c r="W6" s="118"/>
-      <c r="X6" s="118"/>
-      <c r="Y6" s="118"/>
-      <c r="Z6" s="118"/>
-      <c r="AA6" s="118"/>
-      <c r="AB6" s="118"/>
-      <c r="AC6" s="118"/>
-      <c r="AD6" s="118"/>
+      <c r="G6" s="115"/>
+      <c r="H6" s="115"/>
+      <c r="I6" s="115"/>
+      <c r="J6" s="115"/>
+      <c r="K6" s="115"/>
+      <c r="L6" s="115"/>
+      <c r="M6" s="115"/>
+      <c r="N6" s="115"/>
+      <c r="O6" s="115"/>
+      <c r="P6" s="115"/>
+      <c r="Q6" s="115"/>
+      <c r="R6" s="115"/>
+      <c r="S6" s="115"/>
+      <c r="T6" s="115"/>
+      <c r="U6" s="115"/>
+      <c r="V6" s="115"/>
+      <c r="W6" s="115"/>
+      <c r="X6" s="115"/>
+      <c r="Y6" s="115"/>
+      <c r="Z6" s="115"/>
+      <c r="AA6" s="115"/>
+      <c r="AB6" s="115"/>
+      <c r="AC6" s="115"/>
+      <c r="AD6" s="115"/>
       <c r="AE6" s="52"/>
-      <c r="AF6" s="54" t="s">
+      <c r="AF6" s="116" t="s">
         <v>76</v>
       </c>
-      <c r="AG6" s="54"/>
-      <c r="AH6" s="54"/>
-      <c r="AI6" s="54"/>
+      <c r="AG6" s="116"/>
+      <c r="AH6" s="116"/>
+      <c r="AI6" s="116"/>
       <c r="AJ6" s="6"/>
       <c r="AK6" s="1"/>
       <c r="AL6" s="1"/>
@@ -4317,25 +4321,25 @@
     <row r="9" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="107" t="s">
+      <c r="C9" s="106" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="107"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="117">
+      <c r="D9" s="106"/>
+      <c r="E9" s="106"/>
+      <c r="F9" s="118">
         <v>45782</v>
       </c>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="103"/>
-      <c r="J9" s="103"/>
-      <c r="K9" s="103"/>
-      <c r="L9" s="103"/>
-      <c r="M9" s="103"/>
-      <c r="N9" s="103"/>
-      <c r="O9" s="103"/>
-      <c r="P9" s="103"/>
-      <c r="Q9" s="103"/>
+      <c r="G9" s="101"/>
+      <c r="H9" s="101"/>
+      <c r="I9" s="101"/>
+      <c r="J9" s="101"/>
+      <c r="K9" s="101"/>
+      <c r="L9" s="101"/>
+      <c r="M9" s="101"/>
+      <c r="N9" s="101"/>
+      <c r="O9" s="101"/>
+      <c r="P9" s="101"/>
+      <c r="Q9" s="101"/>
       <c r="R9" s="1"/>
       <c r="S9" s="1"/>
       <c r="T9" s="1"/>
@@ -4391,25 +4395,25 @@
     <row r="10" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="5"/>
-      <c r="C10" s="107" t="s">
+      <c r="C10" s="106" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="107"/>
-      <c r="E10" s="107"/>
-      <c r="F10" s="103" t="s">
+      <c r="D10" s="106"/>
+      <c r="E10" s="106"/>
+      <c r="F10" s="101" t="s">
         <v>52</v>
       </c>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
-      <c r="I10" s="103"/>
-      <c r="J10" s="103"/>
-      <c r="K10" s="103"/>
-      <c r="L10" s="103"/>
-      <c r="M10" s="103"/>
-      <c r="N10" s="103"/>
-      <c r="O10" s="103"/>
-      <c r="P10" s="103"/>
-      <c r="Q10" s="103"/>
+      <c r="G10" s="101"/>
+      <c r="H10" s="101"/>
+      <c r="I10" s="101"/>
+      <c r="J10" s="101"/>
+      <c r="K10" s="101"/>
+      <c r="L10" s="101"/>
+      <c r="M10" s="101"/>
+      <c r="N10" s="101"/>
+      <c r="O10" s="101"/>
+      <c r="P10" s="101"/>
+      <c r="Q10" s="101"/>
       <c r="R10" s="1"/>
       <c r="S10" s="1"/>
       <c r="T10" s="1"/>
@@ -4465,25 +4469,25 @@
     <row r="11" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="5"/>
-      <c r="C11" s="107" t="s">
+      <c r="C11" s="106" t="s">
         <v>54</v>
       </c>
-      <c r="D11" s="107"/>
-      <c r="E11" s="107"/>
-      <c r="F11" s="103" t="s">
+      <c r="D11" s="106"/>
+      <c r="E11" s="106"/>
+      <c r="F11" s="101" t="s">
         <v>55</v>
       </c>
-      <c r="G11" s="103"/>
-      <c r="H11" s="103"/>
-      <c r="I11" s="103"/>
-      <c r="J11" s="103"/>
-      <c r="K11" s="103"/>
-      <c r="L11" s="103"/>
-      <c r="M11" s="103"/>
-      <c r="N11" s="103"/>
-      <c r="O11" s="103"/>
-      <c r="P11" s="103"/>
-      <c r="Q11" s="103"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="101"/>
+      <c r="J11" s="101"/>
+      <c r="K11" s="101"/>
+      <c r="L11" s="101"/>
+      <c r="M11" s="101"/>
+      <c r="N11" s="101"/>
+      <c r="O11" s="101"/>
+      <c r="P11" s="101"/>
+      <c r="Q11" s="101"/>
       <c r="R11" s="1"/>
       <c r="S11" s="1"/>
       <c r="T11" s="1"/>
@@ -4687,43 +4691,43 @@
     <row r="14" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="112" t="s">
+      <c r="C14" s="111" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="113"/>
-      <c r="E14" s="113"/>
-      <c r="F14" s="114" t="s">
+      <c r="D14" s="112"/>
+      <c r="E14" s="112"/>
+      <c r="F14" s="113" t="s">
         <v>56</v>
       </c>
-      <c r="G14" s="103"/>
-      <c r="H14" s="103"/>
-      <c r="I14" s="103"/>
-      <c r="J14" s="103"/>
-      <c r="K14" s="103"/>
-      <c r="L14" s="103"/>
-      <c r="M14" s="103"/>
-      <c r="N14" s="103"/>
-      <c r="O14" s="103"/>
-      <c r="P14" s="103"/>
-      <c r="Q14" s="103"/>
-      <c r="R14" s="103"/>
-      <c r="S14" s="103"/>
-      <c r="T14" s="103"/>
-      <c r="U14" s="103"/>
-      <c r="V14" s="103"/>
-      <c r="W14" s="103"/>
-      <c r="X14" s="103"/>
-      <c r="Y14" s="103"/>
-      <c r="Z14" s="103"/>
-      <c r="AA14" s="103"/>
-      <c r="AB14" s="103"/>
-      <c r="AC14" s="103"/>
-      <c r="AD14" s="103"/>
-      <c r="AE14" s="103"/>
-      <c r="AF14" s="103"/>
-      <c r="AG14" s="103"/>
-      <c r="AH14" s="103"/>
-      <c r="AI14" s="103"/>
+      <c r="G14" s="101"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="101"/>
+      <c r="J14" s="101"/>
+      <c r="K14" s="101"/>
+      <c r="L14" s="101"/>
+      <c r="M14" s="101"/>
+      <c r="N14" s="101"/>
+      <c r="O14" s="101"/>
+      <c r="P14" s="101"/>
+      <c r="Q14" s="101"/>
+      <c r="R14" s="101"/>
+      <c r="S14" s="101"/>
+      <c r="T14" s="101"/>
+      <c r="U14" s="101"/>
+      <c r="V14" s="101"/>
+      <c r="W14" s="101"/>
+      <c r="X14" s="101"/>
+      <c r="Y14" s="101"/>
+      <c r="Z14" s="101"/>
+      <c r="AA14" s="101"/>
+      <c r="AB14" s="101"/>
+      <c r="AC14" s="101"/>
+      <c r="AD14" s="101"/>
+      <c r="AE14" s="101"/>
+      <c r="AF14" s="101"/>
+      <c r="AG14" s="101"/>
+      <c r="AH14" s="101"/>
+      <c r="AI14" s="101"/>
       <c r="AJ14" s="6"/>
       <c r="AK14" s="1"/>
       <c r="AL14" s="1"/>
@@ -4765,41 +4769,41 @@
     <row r="15" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="113"/>
-      <c r="D15" s="113"/>
-      <c r="E15" s="113"/>
-      <c r="F15" s="115" t="s">
+      <c r="C15" s="112"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="112"/>
+      <c r="F15" s="114" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="115"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="115"/>
-      <c r="J15" s="115"/>
-      <c r="K15" s="115"/>
-      <c r="L15" s="115"/>
-      <c r="M15" s="115"/>
-      <c r="N15" s="115"/>
-      <c r="O15" s="115"/>
-      <c r="P15" s="115"/>
-      <c r="Q15" s="115"/>
-      <c r="R15" s="115"/>
-      <c r="S15" s="115"/>
-      <c r="T15" s="115"/>
-      <c r="U15" s="115"/>
-      <c r="V15" s="115"/>
-      <c r="W15" s="115"/>
-      <c r="X15" s="115"/>
-      <c r="Y15" s="115"/>
-      <c r="Z15" s="115"/>
-      <c r="AA15" s="115"/>
-      <c r="AB15" s="115"/>
-      <c r="AC15" s="115"/>
-      <c r="AD15" s="115"/>
-      <c r="AE15" s="115"/>
-      <c r="AF15" s="115"/>
-      <c r="AG15" s="115"/>
-      <c r="AH15" s="115"/>
-      <c r="AI15" s="115"/>
+      <c r="G15" s="114"/>
+      <c r="H15" s="114"/>
+      <c r="I15" s="114"/>
+      <c r="J15" s="114"/>
+      <c r="K15" s="114"/>
+      <c r="L15" s="114"/>
+      <c r="M15" s="114"/>
+      <c r="N15" s="114"/>
+      <c r="O15" s="114"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="114"/>
+      <c r="R15" s="114"/>
+      <c r="S15" s="114"/>
+      <c r="T15" s="114"/>
+      <c r="U15" s="114"/>
+      <c r="V15" s="114"/>
+      <c r="W15" s="114"/>
+      <c r="X15" s="114"/>
+      <c r="Y15" s="114"/>
+      <c r="Z15" s="114"/>
+      <c r="AA15" s="114"/>
+      <c r="AB15" s="114"/>
+      <c r="AC15" s="114"/>
+      <c r="AD15" s="114"/>
+      <c r="AE15" s="114"/>
+      <c r="AF15" s="114"/>
+      <c r="AG15" s="114"/>
+      <c r="AH15" s="114"/>
+      <c r="AI15" s="114"/>
       <c r="AJ15" s="6"/>
       <c r="AK15" s="1"/>
       <c r="AL15" s="1"/>
@@ -4837,39 +4841,39 @@
     <row r="16" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="113"/>
-      <c r="D16" s="113"/>
-      <c r="E16" s="113"/>
-      <c r="F16" s="115"/>
-      <c r="G16" s="115"/>
-      <c r="H16" s="115"/>
-      <c r="I16" s="115"/>
-      <c r="J16" s="115"/>
-      <c r="K16" s="115"/>
-      <c r="L16" s="115"/>
-      <c r="M16" s="115"/>
-      <c r="N16" s="115"/>
-      <c r="O16" s="115"/>
-      <c r="P16" s="115"/>
-      <c r="Q16" s="115"/>
-      <c r="R16" s="115"/>
-      <c r="S16" s="115"/>
-      <c r="T16" s="115"/>
-      <c r="U16" s="115"/>
-      <c r="V16" s="115"/>
-      <c r="W16" s="115"/>
-      <c r="X16" s="115"/>
-      <c r="Y16" s="115"/>
-      <c r="Z16" s="115"/>
-      <c r="AA16" s="115"/>
-      <c r="AB16" s="115"/>
-      <c r="AC16" s="115"/>
-      <c r="AD16" s="115"/>
-      <c r="AE16" s="115"/>
-      <c r="AF16" s="115"/>
-      <c r="AG16" s="115"/>
-      <c r="AH16" s="115"/>
-      <c r="AI16" s="115"/>
+      <c r="C16" s="112"/>
+      <c r="D16" s="112"/>
+      <c r="E16" s="112"/>
+      <c r="F16" s="114"/>
+      <c r="G16" s="114"/>
+      <c r="H16" s="114"/>
+      <c r="I16" s="114"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="114"/>
+      <c r="L16" s="114"/>
+      <c r="M16" s="114"/>
+      <c r="N16" s="114"/>
+      <c r="O16" s="114"/>
+      <c r="P16" s="114"/>
+      <c r="Q16" s="114"/>
+      <c r="R16" s="114"/>
+      <c r="S16" s="114"/>
+      <c r="T16" s="114"/>
+      <c r="U16" s="114"/>
+      <c r="V16" s="114"/>
+      <c r="W16" s="114"/>
+      <c r="X16" s="114"/>
+      <c r="Y16" s="114"/>
+      <c r="Z16" s="114"/>
+      <c r="AA16" s="114"/>
+      <c r="AB16" s="114"/>
+      <c r="AC16" s="114"/>
+      <c r="AD16" s="114"/>
+      <c r="AE16" s="114"/>
+      <c r="AF16" s="114"/>
+      <c r="AG16" s="114"/>
+      <c r="AH16" s="114"/>
+      <c r="AI16" s="114"/>
       <c r="AJ16" s="6"/>
       <c r="AK16" s="1"/>
       <c r="AL16" s="1"/>
@@ -4907,39 +4911,39 @@
     <row r="17" spans="1:68" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="113"/>
-      <c r="D17" s="113"/>
-      <c r="E17" s="113"/>
-      <c r="F17" s="115"/>
-      <c r="G17" s="115"/>
-      <c r="H17" s="115"/>
-      <c r="I17" s="115"/>
-      <c r="J17" s="115"/>
-      <c r="K17" s="115"/>
-      <c r="L17" s="115"/>
-      <c r="M17" s="115"/>
-      <c r="N17" s="115"/>
-      <c r="O17" s="115"/>
-      <c r="P17" s="115"/>
-      <c r="Q17" s="115"/>
-      <c r="R17" s="115"/>
-      <c r="S17" s="115"/>
-      <c r="T17" s="115"/>
-      <c r="U17" s="115"/>
-      <c r="V17" s="115"/>
-      <c r="W17" s="115"/>
-      <c r="X17" s="115"/>
-      <c r="Y17" s="115"/>
-      <c r="Z17" s="115"/>
-      <c r="AA17" s="115"/>
-      <c r="AB17" s="115"/>
-      <c r="AC17" s="115"/>
-      <c r="AD17" s="115"/>
-      <c r="AE17" s="115"/>
-      <c r="AF17" s="115"/>
-      <c r="AG17" s="115"/>
-      <c r="AH17" s="115"/>
-      <c r="AI17" s="115"/>
+      <c r="C17" s="112"/>
+      <c r="D17" s="112"/>
+      <c r="E17" s="112"/>
+      <c r="F17" s="114"/>
+      <c r="G17" s="114"/>
+      <c r="H17" s="114"/>
+      <c r="I17" s="114"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="114"/>
+      <c r="L17" s="114"/>
+      <c r="M17" s="114"/>
+      <c r="N17" s="114"/>
+      <c r="O17" s="114"/>
+      <c r="P17" s="114"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="114"/>
+      <c r="T17" s="114"/>
+      <c r="U17" s="114"/>
+      <c r="V17" s="114"/>
+      <c r="W17" s="114"/>
+      <c r="X17" s="114"/>
+      <c r="Y17" s="114"/>
+      <c r="Z17" s="114"/>
+      <c r="AA17" s="114"/>
+      <c r="AB17" s="114"/>
+      <c r="AC17" s="114"/>
+      <c r="AD17" s="114"/>
+      <c r="AE17" s="114"/>
+      <c r="AF17" s="114"/>
+      <c r="AG17" s="114"/>
+      <c r="AH17" s="114"/>
+      <c r="AI17" s="114"/>
       <c r="AJ17" s="6"/>
       <c r="AK17" s="1"/>
       <c r="AL17" s="1"/>
@@ -4977,39 +4981,39 @@
     <row r="18" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="113"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="113"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="115"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="115"/>
-      <c r="J18" s="115"/>
-      <c r="K18" s="115"/>
-      <c r="L18" s="115"/>
-      <c r="M18" s="115"/>
-      <c r="N18" s="115"/>
-      <c r="O18" s="115"/>
-      <c r="P18" s="115"/>
-      <c r="Q18" s="115"/>
-      <c r="R18" s="115"/>
-      <c r="S18" s="115"/>
-      <c r="T18" s="115"/>
-      <c r="U18" s="115"/>
-      <c r="V18" s="115"/>
-      <c r="W18" s="115"/>
-      <c r="X18" s="115"/>
-      <c r="Y18" s="115"/>
-      <c r="Z18" s="115"/>
-      <c r="AA18" s="115"/>
-      <c r="AB18" s="115"/>
-      <c r="AC18" s="115"/>
-      <c r="AD18" s="115"/>
-      <c r="AE18" s="115"/>
-      <c r="AF18" s="115"/>
-      <c r="AG18" s="115"/>
-      <c r="AH18" s="115"/>
-      <c r="AI18" s="115"/>
+      <c r="C18" s="112"/>
+      <c r="D18" s="112"/>
+      <c r="E18" s="112"/>
+      <c r="F18" s="114"/>
+      <c r="G18" s="114"/>
+      <c r="H18" s="114"/>
+      <c r="I18" s="114"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="114"/>
+      <c r="L18" s="114"/>
+      <c r="M18" s="114"/>
+      <c r="N18" s="114"/>
+      <c r="O18" s="114"/>
+      <c r="P18" s="114"/>
+      <c r="Q18" s="114"/>
+      <c r="R18" s="114"/>
+      <c r="S18" s="114"/>
+      <c r="T18" s="114"/>
+      <c r="U18" s="114"/>
+      <c r="V18" s="114"/>
+      <c r="W18" s="114"/>
+      <c r="X18" s="114"/>
+      <c r="Y18" s="114"/>
+      <c r="Z18" s="114"/>
+      <c r="AA18" s="114"/>
+      <c r="AB18" s="114"/>
+      <c r="AC18" s="114"/>
+      <c r="AD18" s="114"/>
+      <c r="AE18" s="114"/>
+      <c r="AF18" s="114"/>
+      <c r="AG18" s="114"/>
+      <c r="AH18" s="114"/>
+      <c r="AI18" s="114"/>
       <c r="AJ18" s="6"/>
       <c r="AK18" s="1"/>
       <c r="AL18" s="1"/>
@@ -5106,12 +5110,12 @@
       <c r="BG19" s="1"/>
       <c r="BH19" s="1"/>
       <c r="BI19" s="7"/>
-      <c r="BJ19" s="116" t="s">
+      <c r="BJ19" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="BK19" s="116"/>
-      <c r="BL19" s="116"/>
-      <c r="BM19" s="116"/>
+      <c r="BK19" s="117"/>
+      <c r="BL19" s="117"/>
+      <c r="BM19" s="117"/>
       <c r="BN19" s="10" t="e">
         <f>+VLOOKUP(F23,BK12:BL14,2,FALSE)</f>
         <v>#N/A</v>
@@ -5122,15 +5126,15 @@
     <row r="20" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="107" t="s">
+      <c r="C20" s="106" t="s">
         <v>5</v>
       </c>
-      <c r="D20" s="107"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="108">
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="107">
         <v>45782</v>
       </c>
-      <c r="G20" s="109"/>
+      <c r="G20" s="108"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
@@ -5204,15 +5208,15 @@
     <row r="21" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="107" t="s">
+      <c r="C21" s="106" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="107"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="108">
+      <c r="D21" s="106"/>
+      <c r="E21" s="106"/>
+      <c r="F21" s="107">
         <v>45860</v>
       </c>
-      <c r="G21" s="109"/>
+      <c r="G21" s="108"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
@@ -5286,15 +5290,15 @@
     <row r="22" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="5"/>
-      <c r="C22" s="107" t="s">
+      <c r="C22" s="106" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="107"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="110">
+      <c r="D22" s="106"/>
+      <c r="E22" s="106"/>
+      <c r="F22" s="109">
         <v>36000000</v>
       </c>
-      <c r="G22" s="110"/>
+      <c r="G22" s="109"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
@@ -5360,15 +5364,15 @@
     <row r="23" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="107" t="s">
+      <c r="C23" s="106" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="111" t="s">
+      <c r="D23" s="106"/>
+      <c r="E23" s="106"/>
+      <c r="F23" s="110" t="s">
         <v>53</v>
       </c>
-      <c r="G23" s="111"/>
+      <c r="G23" s="110"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
       <c r="J23" s="1"/>
@@ -5521,10 +5525,10 @@
     <row r="25" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="5"/>
-      <c r="D25" s="100" t="s">
+      <c r="D25" s="99" t="s">
         <v>16</v>
       </c>
-      <c r="E25" s="101"/>
+      <c r="E25" s="100"/>
       <c r="F25" s="23" t="s">
         <v>17</v>
       </c>
@@ -5611,11 +5615,11 @@
       <c r="C26" s="20">
         <v>0</v>
       </c>
-      <c r="D26" s="105">
+      <c r="D26" s="104">
         <f t="shared" ref="D26:D36" si="4">+BK24</f>
         <v>45782</v>
       </c>
-      <c r="E26" s="106"/>
+      <c r="E26" s="105"/>
       <c r="F26" s="21">
         <v>0</v>
       </c>
@@ -5702,11 +5706,11 @@
       <c r="C27" s="20">
         <v>1</v>
       </c>
-      <c r="D27" s="105">
+      <c r="D27" s="104">
         <f t="shared" si="4"/>
         <v>45789.8</v>
       </c>
-      <c r="E27" s="106"/>
+      <c r="E27" s="105"/>
       <c r="F27" s="21">
         <v>0.04</v>
       </c>
@@ -5793,11 +5797,11 @@
       <c r="C28" s="20">
         <v>2</v>
       </c>
-      <c r="D28" s="105">
+      <c r="D28" s="104">
         <f t="shared" si="4"/>
         <v>45797.599999999999</v>
       </c>
-      <c r="E28" s="106"/>
+      <c r="E28" s="105"/>
       <c r="F28" s="21">
         <v>0.1</v>
       </c>
@@ -5884,11 +5888,11 @@
       <c r="C29" s="20">
         <v>3</v>
       </c>
-      <c r="D29" s="105">
+      <c r="D29" s="104">
         <f t="shared" si="4"/>
         <v>45805.4</v>
       </c>
-      <c r="E29" s="106"/>
+      <c r="E29" s="105"/>
       <c r="F29" s="21">
         <v>0.18</v>
       </c>
@@ -5975,11 +5979,11 @@
       <c r="C30" s="20">
         <v>4</v>
       </c>
-      <c r="D30" s="105">
+      <c r="D30" s="104">
         <f t="shared" si="4"/>
         <v>45813.2</v>
       </c>
-      <c r="E30" s="106"/>
+      <c r="E30" s="105"/>
       <c r="F30" s="21">
         <v>0.28000000000000003</v>
       </c>
@@ -6066,11 +6070,11 @@
       <c r="C31" s="20">
         <v>5</v>
       </c>
-      <c r="D31" s="105">
+      <c r="D31" s="104">
         <f t="shared" si="4"/>
         <v>45821</v>
       </c>
-      <c r="E31" s="106"/>
+      <c r="E31" s="105"/>
       <c r="F31" s="21">
         <v>0.4</v>
       </c>
@@ -6157,11 +6161,11 @@
       <c r="C32" s="20">
         <v>6</v>
       </c>
-      <c r="D32" s="105">
+      <c r="D32" s="104">
         <f t="shared" si="4"/>
         <v>45828.800000000003</v>
       </c>
-      <c r="E32" s="106"/>
+      <c r="E32" s="105"/>
       <c r="F32" s="21">
         <v>0.55000000000000004</v>
       </c>
@@ -6248,11 +6252,11 @@
       <c r="C33" s="20">
         <v>7</v>
       </c>
-      <c r="D33" s="105">
+      <c r="D33" s="104">
         <f t="shared" si="4"/>
         <v>45836.6</v>
       </c>
-      <c r="E33" s="106"/>
+      <c r="E33" s="105"/>
       <c r="F33" s="21">
         <v>0.75</v>
       </c>
@@ -6339,11 +6343,11 @@
       <c r="C34" s="20">
         <v>8</v>
       </c>
-      <c r="D34" s="105">
+      <c r="D34" s="104">
         <f t="shared" si="4"/>
         <v>45844.4</v>
       </c>
-      <c r="E34" s="106"/>
+      <c r="E34" s="105"/>
       <c r="F34" s="21">
         <v>0.93</v>
       </c>
@@ -6430,11 +6434,11 @@
       <c r="C35" s="20">
         <v>9</v>
       </c>
-      <c r="D35" s="105">
+      <c r="D35" s="104">
         <f t="shared" si="4"/>
         <v>45852.2</v>
       </c>
-      <c r="E35" s="106"/>
+      <c r="E35" s="105"/>
       <c r="F35" s="21">
         <v>0.99</v>
       </c>
@@ -6507,11 +6511,11 @@
       <c r="C36" s="20">
         <v>10</v>
       </c>
-      <c r="D36" s="105">
+      <c r="D36" s="104">
         <f t="shared" si="4"/>
         <v>45860</v>
       </c>
-      <c r="E36" s="106"/>
+      <c r="E36" s="105"/>
       <c r="F36" s="21">
         <v>1</v>
       </c>
@@ -6649,10 +6653,10 @@
     <row r="38" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="5"/>
-      <c r="D38" s="100" t="s">
+      <c r="D38" s="99" t="s">
         <v>19</v>
       </c>
-      <c r="E38" s="101"/>
+      <c r="E38" s="100"/>
       <c r="F38" s="50">
         <f>+MAX(F26:F36)</f>
         <v>1</v>
@@ -6665,35 +6669,35 @@
         <v>20</v>
       </c>
       <c r="I38" s="73"/>
-      <c r="J38" s="103" t="str">
+      <c r="J38" s="101" t="str">
         <f>+ CONCATENATE(100*(100%-F38),"% del alcance del proyecto y ",(100%-G38)*100,"% del Presupuesto, con saldo =   $ ",(F22-SUM(G26:G36))/1000000," Millones.")</f>
         <v>0% del alcance del proyecto y 0% del Presupuesto, con saldo =   $ 0 Millones.</v>
       </c>
-      <c r="K38" s="103"/>
-      <c r="L38" s="103"/>
-      <c r="M38" s="103"/>
-      <c r="N38" s="103"/>
-      <c r="O38" s="103"/>
-      <c r="P38" s="103"/>
-      <c r="Q38" s="103"/>
-      <c r="R38" s="103"/>
-      <c r="S38" s="103"/>
-      <c r="T38" s="103"/>
-      <c r="U38" s="103"/>
-      <c r="V38" s="103"/>
-      <c r="W38" s="103"/>
-      <c r="X38" s="103"/>
-      <c r="Y38" s="103"/>
-      <c r="Z38" s="103"/>
-      <c r="AA38" s="103"/>
-      <c r="AB38" s="103"/>
-      <c r="AC38" s="103"/>
-      <c r="AD38" s="103"/>
-      <c r="AE38" s="103"/>
-      <c r="AF38" s="103"/>
-      <c r="AG38" s="103"/>
-      <c r="AH38" s="103"/>
-      <c r="AI38" s="103"/>
+      <c r="K38" s="101"/>
+      <c r="L38" s="101"/>
+      <c r="M38" s="101"/>
+      <c r="N38" s="101"/>
+      <c r="O38" s="101"/>
+      <c r="P38" s="101"/>
+      <c r="Q38" s="101"/>
+      <c r="R38" s="101"/>
+      <c r="S38" s="101"/>
+      <c r="T38" s="101"/>
+      <c r="U38" s="101"/>
+      <c r="V38" s="101"/>
+      <c r="W38" s="101"/>
+      <c r="X38" s="101"/>
+      <c r="Y38" s="101"/>
+      <c r="Z38" s="101"/>
+      <c r="AA38" s="101"/>
+      <c r="AB38" s="101"/>
+      <c r="AC38" s="101"/>
+      <c r="AD38" s="101"/>
+      <c r="AE38" s="101"/>
+      <c r="AF38" s="101"/>
+      <c r="AG38" s="101"/>
+      <c r="AH38" s="101"/>
+      <c r="AI38" s="101"/>
       <c r="AJ38" s="6"/>
       <c r="AK38" s="1"/>
       <c r="AL38" s="1"/>
@@ -6936,68 +6940,68 @@
       <c r="C42" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="100" t="s">
+      <c r="D42" s="99" t="s">
         <v>22</v>
       </c>
-      <c r="E42" s="104"/>
-      <c r="F42" s="104"/>
-      <c r="G42" s="101"/>
-      <c r="H42" s="100" t="s">
+      <c r="E42" s="102"/>
+      <c r="F42" s="102"/>
+      <c r="G42" s="100"/>
+      <c r="H42" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="I42" s="101"/>
-      <c r="J42" s="100" t="s">
+      <c r="I42" s="100"/>
+      <c r="J42" s="99" t="s">
         <v>24</v>
       </c>
-      <c r="K42" s="101"/>
-      <c r="L42" s="100" t="s">
+      <c r="K42" s="100"/>
+      <c r="L42" s="99" t="s">
         <v>25</v>
       </c>
-      <c r="M42" s="101"/>
-      <c r="N42" s="100" t="s">
+      <c r="M42" s="100"/>
+      <c r="N42" s="99" t="s">
         <v>26</v>
       </c>
-      <c r="O42" s="101"/>
-      <c r="P42" s="100" t="s">
+      <c r="O42" s="100"/>
+      <c r="P42" s="99" t="s">
         <v>27</v>
       </c>
-      <c r="Q42" s="101"/>
-      <c r="R42" s="100" t="s">
+      <c r="Q42" s="100"/>
+      <c r="R42" s="99" t="s">
         <v>28</v>
       </c>
-      <c r="S42" s="101"/>
-      <c r="T42" s="100" t="s">
+      <c r="S42" s="100"/>
+      <c r="T42" s="99" t="s">
         <v>29</v>
       </c>
-      <c r="U42" s="101"/>
-      <c r="V42" s="100" t="s">
+      <c r="U42" s="100"/>
+      <c r="V42" s="99" t="s">
         <v>30</v>
       </c>
-      <c r="W42" s="101"/>
-      <c r="X42" s="100" t="s">
+      <c r="W42" s="100"/>
+      <c r="X42" s="99" t="s">
         <v>31</v>
       </c>
-      <c r="Y42" s="101"/>
-      <c r="Z42" s="100" t="s">
+      <c r="Y42" s="100"/>
+      <c r="Z42" s="99" t="s">
         <v>32</v>
       </c>
-      <c r="AA42" s="101"/>
-      <c r="AB42" s="100" t="s">
+      <c r="AA42" s="100"/>
+      <c r="AB42" s="99" t="s">
         <v>33</v>
       </c>
-      <c r="AC42" s="101"/>
-      <c r="AD42" s="100" t="s">
+      <c r="AC42" s="100"/>
+      <c r="AD42" s="99" t="s">
         <v>34</v>
       </c>
-      <c r="AE42" s="101"/>
-      <c r="AF42" s="100" t="s">
+      <c r="AE42" s="100"/>
+      <c r="AF42" s="99" t="s">
         <v>35</v>
       </c>
-      <c r="AG42" s="101"/>
-      <c r="AH42" s="102" t="s">
+      <c r="AG42" s="100"/>
+      <c r="AH42" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="AI42" s="102"/>
+      <c r="AI42" s="103"/>
       <c r="AJ42" s="6"/>
       <c r="AK42" s="1"/>
       <c r="AL42" s="1"/>
@@ -7033,53 +7037,53 @@
     <row r="43" spans="1:66" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="85">
+      <c r="C43" s="79">
         <v>2025</v>
       </c>
       <c r="D43" s="24">
         <v>1</v>
       </c>
-      <c r="E43" s="77" t="s">
+      <c r="E43" s="76" t="s">
         <v>59</v>
       </c>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
       <c r="H43" s="25">
         <v>3000000</v>
       </c>
       <c r="I43" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="J43" s="97"/>
-      <c r="K43" s="98"/>
-      <c r="L43" s="97"/>
-      <c r="M43" s="98"/>
-      <c r="N43" s="97"/>
-      <c r="O43" s="98"/>
-      <c r="P43" s="97"/>
-      <c r="Q43" s="98"/>
-      <c r="R43" s="97">
+      <c r="J43" s="94"/>
+      <c r="K43" s="95"/>
+      <c r="L43" s="94"/>
+      <c r="M43" s="95"/>
+      <c r="N43" s="94"/>
+      <c r="O43" s="95"/>
+      <c r="P43" s="94"/>
+      <c r="Q43" s="95"/>
+      <c r="R43" s="94">
         <v>1</v>
       </c>
-      <c r="S43" s="98"/>
-      <c r="T43" s="97"/>
-      <c r="U43" s="98"/>
-      <c r="V43" s="97"/>
-      <c r="W43" s="98"/>
-      <c r="X43" s="97"/>
-      <c r="Y43" s="98"/>
-      <c r="Z43" s="97"/>
-      <c r="AA43" s="98"/>
-      <c r="AB43" s="97"/>
-      <c r="AC43" s="98"/>
-      <c r="AD43" s="97"/>
-      <c r="AE43" s="98"/>
-      <c r="AF43" s="97"/>
-      <c r="AG43" s="98"/>
-      <c r="AH43" s="83">
+      <c r="S43" s="95"/>
+      <c r="T43" s="94"/>
+      <c r="U43" s="95"/>
+      <c r="V43" s="94"/>
+      <c r="W43" s="95"/>
+      <c r="X43" s="94"/>
+      <c r="Y43" s="95"/>
+      <c r="Z43" s="94"/>
+      <c r="AA43" s="95"/>
+      <c r="AB43" s="94"/>
+      <c r="AC43" s="95"/>
+      <c r="AD43" s="94"/>
+      <c r="AE43" s="95"/>
+      <c r="AF43" s="94"/>
+      <c r="AG43" s="95"/>
+      <c r="AH43" s="84">
         <v>1</v>
       </c>
-      <c r="AI43" s="84"/>
+      <c r="AI43" s="85"/>
       <c r="AJ43" s="6"/>
       <c r="AK43" s="1"/>
       <c r="AL43" s="1"/>
@@ -7115,55 +7119,55 @@
     <row r="44" spans="1:66" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="5"/>
-      <c r="C44" s="86"/>
+      <c r="C44" s="80"/>
       <c r="D44" s="27">
         <v>2</v>
       </c>
-      <c r="E44" s="77" t="s">
+      <c r="E44" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
       <c r="H44" s="25">
         <v>15000000</v>
       </c>
       <c r="I44" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="J44" s="97"/>
-      <c r="K44" s="98"/>
-      <c r="L44" s="97"/>
-      <c r="M44" s="98"/>
-      <c r="N44" s="97"/>
-      <c r="O44" s="98"/>
-      <c r="P44" s="97"/>
-      <c r="Q44" s="98"/>
-      <c r="R44" s="97">
+      <c r="J44" s="94"/>
+      <c r="K44" s="95"/>
+      <c r="L44" s="94"/>
+      <c r="M44" s="95"/>
+      <c r="N44" s="94"/>
+      <c r="O44" s="95"/>
+      <c r="P44" s="94"/>
+      <c r="Q44" s="95"/>
+      <c r="R44" s="94">
         <v>0.25</v>
       </c>
-      <c r="S44" s="98"/>
-      <c r="T44" s="97">
+      <c r="S44" s="95"/>
+      <c r="T44" s="94">
         <v>0.75</v>
       </c>
-      <c r="U44" s="98"/>
-      <c r="V44" s="97">
+      <c r="U44" s="95"/>
+      <c r="V44" s="94">
         <v>1</v>
       </c>
-      <c r="W44" s="98"/>
-      <c r="X44" s="97"/>
-      <c r="Y44" s="98"/>
-      <c r="Z44" s="97"/>
-      <c r="AA44" s="98"/>
-      <c r="AB44" s="97"/>
-      <c r="AC44" s="98"/>
-      <c r="AD44" s="97"/>
-      <c r="AE44" s="98"/>
-      <c r="AF44" s="97"/>
-      <c r="AG44" s="98"/>
-      <c r="AH44" s="80">
+      <c r="W44" s="95"/>
+      <c r="X44" s="94"/>
+      <c r="Y44" s="95"/>
+      <c r="Z44" s="94"/>
+      <c r="AA44" s="95"/>
+      <c r="AB44" s="94"/>
+      <c r="AC44" s="95"/>
+      <c r="AD44" s="94"/>
+      <c r="AE44" s="95"/>
+      <c r="AF44" s="94"/>
+      <c r="AG44" s="95"/>
+      <c r="AH44" s="83">
         <v>1</v>
       </c>
-      <c r="AI44" s="80"/>
+      <c r="AI44" s="83"/>
       <c r="AJ44" s="6"/>
       <c r="AK44" s="1"/>
       <c r="AL44" s="1"/>
@@ -7199,49 +7203,49 @@
     <row r="45" spans="1:66" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="5"/>
-      <c r="C45" s="86"/>
+      <c r="C45" s="80"/>
       <c r="D45" s="27">
         <v>3</v>
       </c>
-      <c r="E45" s="77" t="s">
+      <c r="E45" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="F45" s="77"/>
-      <c r="G45" s="77"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="76"/>
       <c r="H45" s="25">
         <v>12000000</v>
       </c>
       <c r="I45" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="J45" s="97"/>
-      <c r="K45" s="98"/>
-      <c r="L45" s="97"/>
-      <c r="M45" s="98"/>
-      <c r="N45" s="97"/>
-      <c r="O45" s="98"/>
-      <c r="P45" s="97"/>
-      <c r="Q45" s="98"/>
-      <c r="R45" s="97"/>
-      <c r="S45" s="98"/>
-      <c r="T45" s="97">
+      <c r="J45" s="94"/>
+      <c r="K45" s="95"/>
+      <c r="L45" s="94"/>
+      <c r="M45" s="95"/>
+      <c r="N45" s="94"/>
+      <c r="O45" s="95"/>
+      <c r="P45" s="94"/>
+      <c r="Q45" s="95"/>
+      <c r="R45" s="94"/>
+      <c r="S45" s="95"/>
+      <c r="T45" s="94">
         <v>0.3</v>
       </c>
-      <c r="U45" s="98"/>
-      <c r="V45" s="97">
+      <c r="U45" s="95"/>
+      <c r="V45" s="94">
         <v>1</v>
       </c>
-      <c r="W45" s="98"/>
-      <c r="X45" s="97"/>
-      <c r="Y45" s="98"/>
-      <c r="Z45" s="97"/>
-      <c r="AA45" s="98"/>
-      <c r="AB45" s="97"/>
-      <c r="AC45" s="98"/>
-      <c r="AD45" s="97"/>
-      <c r="AE45" s="98"/>
-      <c r="AF45" s="97"/>
-      <c r="AG45" s="98"/>
+      <c r="W45" s="95"/>
+      <c r="X45" s="94"/>
+      <c r="Y45" s="95"/>
+      <c r="Z45" s="94"/>
+      <c r="AA45" s="95"/>
+      <c r="AB45" s="94"/>
+      <c r="AC45" s="95"/>
+      <c r="AD45" s="94"/>
+      <c r="AE45" s="95"/>
+      <c r="AF45" s="94"/>
+      <c r="AG45" s="95"/>
       <c r="AH45" s="74">
         <v>1</v>
       </c>
@@ -7281,50 +7285,50 @@
     <row r="46" spans="1:66" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="78">
+      <c r="C46" s="77">
         <f>+SUM(H43:H46)</f>
         <v>36000000</v>
       </c>
       <c r="D46" s="27">
         <v>4</v>
       </c>
-      <c r="E46" s="77" t="s">
+      <c r="E46" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="F46" s="77"/>
-      <c r="G46" s="77"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="76"/>
       <c r="H46" s="25">
         <v>6000000</v>
       </c>
       <c r="I46" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="J46" s="97"/>
-      <c r="K46" s="98"/>
-      <c r="L46" s="97"/>
-      <c r="M46" s="98"/>
-      <c r="N46" s="97"/>
-      <c r="O46" s="98"/>
-      <c r="P46" s="97"/>
-      <c r="Q46" s="98"/>
-      <c r="R46" s="97"/>
-      <c r="S46" s="98"/>
-      <c r="T46" s="97"/>
-      <c r="U46" s="98"/>
-      <c r="V46" s="97">
+      <c r="J46" s="94"/>
+      <c r="K46" s="95"/>
+      <c r="L46" s="94"/>
+      <c r="M46" s="95"/>
+      <c r="N46" s="94"/>
+      <c r="O46" s="95"/>
+      <c r="P46" s="94"/>
+      <c r="Q46" s="95"/>
+      <c r="R46" s="94"/>
+      <c r="S46" s="95"/>
+      <c r="T46" s="94"/>
+      <c r="U46" s="95"/>
+      <c r="V46" s="94">
         <v>1</v>
       </c>
-      <c r="W46" s="98"/>
-      <c r="X46" s="97"/>
-      <c r="Y46" s="98"/>
-      <c r="Z46" s="97"/>
-      <c r="AA46" s="98"/>
-      <c r="AB46" s="97"/>
-      <c r="AC46" s="98"/>
-      <c r="AD46" s="97"/>
-      <c r="AE46" s="98"/>
-      <c r="AF46" s="97"/>
-      <c r="AG46" s="98"/>
+      <c r="W46" s="95"/>
+      <c r="X46" s="94"/>
+      <c r="Y46" s="95"/>
+      <c r="Z46" s="94"/>
+      <c r="AA46" s="95"/>
+      <c r="AB46" s="94"/>
+      <c r="AC46" s="95"/>
+      <c r="AD46" s="94"/>
+      <c r="AE46" s="95"/>
+      <c r="AF46" s="94"/>
+      <c r="AG46" s="95"/>
       <c r="AH46" s="74">
         <v>1</v>
       </c>
@@ -7362,47 +7366,47 @@
     <row r="47" spans="1:66" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="1"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="91"/>
+      <c r="C47" s="90"/>
       <c r="D47" s="28">
         <v>5</v>
       </c>
-      <c r="E47" s="99" t="s">
+      <c r="E47" s="96" t="s">
         <v>62</v>
       </c>
-      <c r="F47" s="99"/>
-      <c r="G47" s="99"/>
+      <c r="F47" s="96"/>
+      <c r="G47" s="96"/>
       <c r="H47" s="29">
         <v>100</v>
       </c>
       <c r="I47" s="30" t="s">
         <v>38</v>
       </c>
-      <c r="J47" s="95"/>
-      <c r="K47" s="96"/>
-      <c r="L47" s="95"/>
-      <c r="M47" s="96"/>
-      <c r="N47" s="95"/>
-      <c r="O47" s="96"/>
-      <c r="P47" s="95"/>
-      <c r="Q47" s="96"/>
-      <c r="R47" s="95"/>
-      <c r="S47" s="96"/>
-      <c r="T47" s="95"/>
-      <c r="U47" s="96"/>
-      <c r="V47" s="95">
+      <c r="J47" s="97"/>
+      <c r="K47" s="98"/>
+      <c r="L47" s="97"/>
+      <c r="M47" s="98"/>
+      <c r="N47" s="97"/>
+      <c r="O47" s="98"/>
+      <c r="P47" s="97"/>
+      <c r="Q47" s="98"/>
+      <c r="R47" s="97"/>
+      <c r="S47" s="98"/>
+      <c r="T47" s="97"/>
+      <c r="U47" s="98"/>
+      <c r="V47" s="97">
         <v>1</v>
       </c>
-      <c r="W47" s="96"/>
-      <c r="X47" s="95"/>
-      <c r="Y47" s="96"/>
-      <c r="Z47" s="95"/>
-      <c r="AA47" s="96"/>
-      <c r="AB47" s="95"/>
-      <c r="AC47" s="96"/>
-      <c r="AD47" s="95"/>
-      <c r="AE47" s="96"/>
-      <c r="AF47" s="95"/>
-      <c r="AG47" s="96"/>
+      <c r="W47" s="98"/>
+      <c r="X47" s="97"/>
+      <c r="Y47" s="98"/>
+      <c r="Z47" s="97"/>
+      <c r="AA47" s="98"/>
+      <c r="AB47" s="97"/>
+      <c r="AC47" s="98"/>
+      <c r="AD47" s="97"/>
+      <c r="AE47" s="98"/>
+      <c r="AF47" s="97"/>
+      <c r="AG47" s="98"/>
       <c r="AH47" s="74">
         <v>1</v>
       </c>
@@ -7442,41 +7446,41 @@
     <row r="48" spans="1:66" ht="3" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="5"/>
-      <c r="C48" s="85"/>
+      <c r="C48" s="79"/>
       <c r="D48" s="31">
         <v>1</v>
       </c>
-      <c r="E48" s="94"/>
-      <c r="F48" s="94"/>
-      <c r="G48" s="94"/>
+      <c r="E48" s="93"/>
+      <c r="F48" s="93"/>
+      <c r="G48" s="93"/>
       <c r="H48" s="32"/>
       <c r="I48" s="33"/>
-      <c r="J48" s="92"/>
-      <c r="K48" s="93"/>
-      <c r="L48" s="92"/>
-      <c r="M48" s="93"/>
-      <c r="N48" s="92"/>
-      <c r="O48" s="93"/>
-      <c r="P48" s="92"/>
-      <c r="Q48" s="93"/>
-      <c r="R48" s="92"/>
-      <c r="S48" s="93"/>
-      <c r="T48" s="92"/>
-      <c r="U48" s="93"/>
-      <c r="V48" s="92"/>
-      <c r="W48" s="93"/>
-      <c r="X48" s="92"/>
-      <c r="Y48" s="93"/>
-      <c r="Z48" s="92"/>
-      <c r="AA48" s="93"/>
-      <c r="AB48" s="92"/>
-      <c r="AC48" s="93"/>
-      <c r="AD48" s="92"/>
-      <c r="AE48" s="93"/>
-      <c r="AF48" s="92"/>
-      <c r="AG48" s="93"/>
-      <c r="AH48" s="83"/>
-      <c r="AI48" s="84"/>
+      <c r="J48" s="91"/>
+      <c r="K48" s="92"/>
+      <c r="L48" s="91"/>
+      <c r="M48" s="92"/>
+      <c r="N48" s="91"/>
+      <c r="O48" s="92"/>
+      <c r="P48" s="91"/>
+      <c r="Q48" s="92"/>
+      <c r="R48" s="91"/>
+      <c r="S48" s="92"/>
+      <c r="T48" s="91"/>
+      <c r="U48" s="92"/>
+      <c r="V48" s="91"/>
+      <c r="W48" s="92"/>
+      <c r="X48" s="91"/>
+      <c r="Y48" s="92"/>
+      <c r="Z48" s="91"/>
+      <c r="AA48" s="92"/>
+      <c r="AB48" s="91"/>
+      <c r="AC48" s="92"/>
+      <c r="AD48" s="91"/>
+      <c r="AE48" s="92"/>
+      <c r="AF48" s="91"/>
+      <c r="AG48" s="92"/>
+      <c r="AH48" s="84"/>
+      <c r="AI48" s="85"/>
       <c r="AJ48" s="6"/>
       <c r="AK48" s="1"/>
       <c r="AL48" s="1"/>
@@ -7512,13 +7516,13 @@
     <row r="49" spans="1:66" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="5"/>
-      <c r="C49" s="86"/>
+      <c r="C49" s="80"/>
       <c r="D49" s="27">
         <v>2</v>
       </c>
-      <c r="E49" s="77"/>
-      <c r="F49" s="77"/>
-      <c r="G49" s="77"/>
+      <c r="E49" s="76"/>
+      <c r="F49" s="76"/>
+      <c r="G49" s="76"/>
       <c r="H49" s="25"/>
       <c r="I49" s="26"/>
       <c r="J49" s="72"/>
@@ -7545,8 +7549,8 @@
       <c r="AE49" s="73"/>
       <c r="AF49" s="72"/>
       <c r="AG49" s="73"/>
-      <c r="AH49" s="80"/>
-      <c r="AI49" s="80"/>
+      <c r="AH49" s="83"/>
+      <c r="AI49" s="83"/>
       <c r="AJ49" s="6"/>
       <c r="AK49" s="1"/>
       <c r="AL49" s="1"/>
@@ -7582,13 +7586,13 @@
     <row r="50" spans="1:66" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="5"/>
-      <c r="C50" s="86"/>
+      <c r="C50" s="80"/>
       <c r="D50" s="27">
         <v>3</v>
       </c>
-      <c r="E50" s="77"/>
-      <c r="F50" s="77"/>
-      <c r="G50" s="77"/>
+      <c r="E50" s="76"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="76"/>
       <c r="H50" s="25"/>
       <c r="I50" s="26"/>
       <c r="J50" s="72"/>
@@ -7652,13 +7656,13 @@
     <row r="51" spans="1:66" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="78"/>
+      <c r="C51" s="77"/>
       <c r="D51" s="27">
         <v>4</v>
       </c>
-      <c r="E51" s="77"/>
-      <c r="F51" s="77"/>
-      <c r="G51" s="77"/>
+      <c r="E51" s="76"/>
+      <c r="F51" s="76"/>
+      <c r="G51" s="76"/>
       <c r="H51" s="25"/>
       <c r="I51" s="26"/>
       <c r="J51" s="72"/>
@@ -7722,13 +7726,13 @@
     <row r="52" spans="1:66" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="1"/>
       <c r="B52" s="5"/>
-      <c r="C52" s="91"/>
+      <c r="C52" s="90"/>
       <c r="D52" s="34">
         <v>5</v>
       </c>
-      <c r="E52" s="90"/>
-      <c r="F52" s="90"/>
-      <c r="G52" s="90"/>
+      <c r="E52" s="87"/>
+      <c r="F52" s="87"/>
+      <c r="G52" s="87"/>
       <c r="H52" s="35"/>
       <c r="I52" s="36"/>
       <c r="J52" s="88"/>
@@ -7792,41 +7796,41 @@
     <row r="53" spans="1:66" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="5"/>
-      <c r="C53" s="85"/>
+      <c r="C53" s="79"/>
       <c r="D53" s="31">
         <v>1</v>
       </c>
-      <c r="E53" s="94"/>
-      <c r="F53" s="94"/>
-      <c r="G53" s="94"/>
+      <c r="E53" s="93"/>
+      <c r="F53" s="93"/>
+      <c r="G53" s="93"/>
       <c r="H53" s="32"/>
       <c r="I53" s="33"/>
-      <c r="J53" s="92"/>
-      <c r="K53" s="93"/>
-      <c r="L53" s="92"/>
-      <c r="M53" s="93"/>
-      <c r="N53" s="92"/>
-      <c r="O53" s="93"/>
-      <c r="P53" s="92"/>
-      <c r="Q53" s="93"/>
-      <c r="R53" s="92"/>
-      <c r="S53" s="93"/>
-      <c r="T53" s="92"/>
-      <c r="U53" s="93"/>
-      <c r="V53" s="92"/>
-      <c r="W53" s="93"/>
-      <c r="X53" s="92"/>
-      <c r="Y53" s="93"/>
-      <c r="Z53" s="92"/>
-      <c r="AA53" s="93"/>
-      <c r="AB53" s="92"/>
-      <c r="AC53" s="93"/>
-      <c r="AD53" s="92"/>
-      <c r="AE53" s="93"/>
-      <c r="AF53" s="92"/>
-      <c r="AG53" s="93"/>
-      <c r="AH53" s="83"/>
-      <c r="AI53" s="84"/>
+      <c r="J53" s="91"/>
+      <c r="K53" s="92"/>
+      <c r="L53" s="91"/>
+      <c r="M53" s="92"/>
+      <c r="N53" s="91"/>
+      <c r="O53" s="92"/>
+      <c r="P53" s="91"/>
+      <c r="Q53" s="92"/>
+      <c r="R53" s="91"/>
+      <c r="S53" s="92"/>
+      <c r="T53" s="91"/>
+      <c r="U53" s="92"/>
+      <c r="V53" s="91"/>
+      <c r="W53" s="92"/>
+      <c r="X53" s="91"/>
+      <c r="Y53" s="92"/>
+      <c r="Z53" s="91"/>
+      <c r="AA53" s="92"/>
+      <c r="AB53" s="91"/>
+      <c r="AC53" s="92"/>
+      <c r="AD53" s="91"/>
+      <c r="AE53" s="92"/>
+      <c r="AF53" s="91"/>
+      <c r="AG53" s="92"/>
+      <c r="AH53" s="84"/>
+      <c r="AI53" s="85"/>
       <c r="AJ53" s="6"/>
       <c r="AK53" s="1"/>
       <c r="AL53" s="1"/>
@@ -7862,13 +7866,13 @@
     <row r="54" spans="1:66" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="5"/>
-      <c r="C54" s="86"/>
+      <c r="C54" s="80"/>
       <c r="D54" s="27">
         <v>2</v>
       </c>
-      <c r="E54" s="77"/>
-      <c r="F54" s="77"/>
-      <c r="G54" s="77"/>
+      <c r="E54" s="76"/>
+      <c r="F54" s="76"/>
+      <c r="G54" s="76"/>
       <c r="H54" s="25"/>
       <c r="I54" s="26"/>
       <c r="J54" s="72"/>
@@ -7895,8 +7899,8 @@
       <c r="AE54" s="73"/>
       <c r="AF54" s="72"/>
       <c r="AG54" s="73"/>
-      <c r="AH54" s="80"/>
-      <c r="AI54" s="80"/>
+      <c r="AH54" s="83"/>
+      <c r="AI54" s="83"/>
       <c r="AJ54" s="6"/>
       <c r="AK54" s="1"/>
       <c r="AL54" s="1"/>
@@ -7932,13 +7936,13 @@
     <row r="55" spans="1:66" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="5"/>
-      <c r="C55" s="86"/>
+      <c r="C55" s="80"/>
       <c r="D55" s="27">
         <v>3</v>
       </c>
-      <c r="E55" s="77"/>
-      <c r="F55" s="77"/>
-      <c r="G55" s="77"/>
+      <c r="E55" s="76"/>
+      <c r="F55" s="76"/>
+      <c r="G55" s="76"/>
       <c r="H55" s="25"/>
       <c r="I55" s="26"/>
       <c r="J55" s="72"/>
@@ -8002,13 +8006,13 @@
     <row r="56" spans="1:66" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="5"/>
-      <c r="C56" s="78"/>
+      <c r="C56" s="77"/>
       <c r="D56" s="27">
         <v>4</v>
       </c>
-      <c r="E56" s="77"/>
-      <c r="F56" s="77"/>
-      <c r="G56" s="77"/>
+      <c r="E56" s="76"/>
+      <c r="F56" s="76"/>
+      <c r="G56" s="76"/>
       <c r="H56" s="25"/>
       <c r="I56" s="26"/>
       <c r="J56" s="72"/>
@@ -8072,13 +8076,13 @@
     <row r="57" spans="1:66" ht="30" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A57" s="1"/>
       <c r="B57" s="5"/>
-      <c r="C57" s="91"/>
+      <c r="C57" s="90"/>
       <c r="D57" s="34">
         <v>5</v>
       </c>
-      <c r="E57" s="90"/>
-      <c r="F57" s="90"/>
-      <c r="G57" s="90"/>
+      <c r="E57" s="87"/>
+      <c r="F57" s="87"/>
+      <c r="G57" s="87"/>
       <c r="H57" s="40"/>
       <c r="I57" s="36"/>
       <c r="J57" s="88"/>
@@ -8141,13 +8145,13 @@
     <row r="58" spans="1:66" ht="30" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="5"/>
-      <c r="C58" s="85"/>
+      <c r="C58" s="79"/>
       <c r="D58" s="24">
         <v>1</v>
       </c>
-      <c r="E58" s="87"/>
-      <c r="F58" s="87"/>
-      <c r="G58" s="87"/>
+      <c r="E58" s="86"/>
+      <c r="F58" s="86"/>
+      <c r="G58" s="86"/>
       <c r="H58" s="41"/>
       <c r="I58" s="42"/>
       <c r="J58" s="81"/>
@@ -8174,8 +8178,8 @@
       <c r="AE58" s="82"/>
       <c r="AF58" s="81"/>
       <c r="AG58" s="82"/>
-      <c r="AH58" s="83"/>
-      <c r="AI58" s="84"/>
+      <c r="AH58" s="84"/>
+      <c r="AI58" s="85"/>
       <c r="AJ58" s="6"/>
       <c r="AK58" s="1"/>
       <c r="AL58" s="1"/>
@@ -8211,13 +8215,13 @@
     <row r="59" spans="1:66" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="5"/>
-      <c r="C59" s="86"/>
+      <c r="C59" s="80"/>
       <c r="D59" s="27">
         <v>2</v>
       </c>
-      <c r="E59" s="77"/>
-      <c r="F59" s="77"/>
-      <c r="G59" s="77"/>
+      <c r="E59" s="76"/>
+      <c r="F59" s="76"/>
+      <c r="G59" s="76"/>
       <c r="H59" s="25"/>
       <c r="I59" s="26"/>
       <c r="J59" s="72"/>
@@ -8244,8 +8248,8 @@
       <c r="AE59" s="73"/>
       <c r="AF59" s="72"/>
       <c r="AG59" s="73"/>
-      <c r="AH59" s="80"/>
-      <c r="AI59" s="80"/>
+      <c r="AH59" s="83"/>
+      <c r="AI59" s="83"/>
       <c r="AJ59" s="6"/>
       <c r="AK59" s="1"/>
       <c r="AL59" s="1"/>
@@ -8280,13 +8284,13 @@
     <row r="60" spans="1:66" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1"/>
       <c r="B60" s="5"/>
-      <c r="C60" s="86"/>
+      <c r="C60" s="80"/>
       <c r="D60" s="27">
         <v>3</v>
       </c>
-      <c r="E60" s="77"/>
-      <c r="F60" s="77"/>
-      <c r="G60" s="77"/>
+      <c r="E60" s="76"/>
+      <c r="F60" s="76"/>
+      <c r="G60" s="76"/>
       <c r="H60" s="25"/>
       <c r="I60" s="26"/>
       <c r="J60" s="72"/>
@@ -8350,13 +8354,13 @@
     <row r="61" spans="1:66" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1"/>
       <c r="B61" s="5"/>
-      <c r="C61" s="78"/>
+      <c r="C61" s="77"/>
       <c r="D61" s="27">
         <v>4</v>
       </c>
-      <c r="E61" s="77"/>
-      <c r="F61" s="77"/>
-      <c r="G61" s="77"/>
+      <c r="E61" s="76"/>
+      <c r="F61" s="76"/>
+      <c r="G61" s="76"/>
       <c r="H61" s="25"/>
       <c r="I61" s="26"/>
       <c r="J61" s="72"/>
@@ -8420,13 +8424,13 @@
     <row r="62" spans="1:66" ht="30" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1"/>
       <c r="B62" s="5"/>
-      <c r="C62" s="79"/>
+      <c r="C62" s="78"/>
       <c r="D62" s="27">
         <v>5</v>
       </c>
-      <c r="E62" s="77"/>
-      <c r="F62" s="77"/>
-      <c r="G62" s="77"/>
+      <c r="E62" s="76"/>
+      <c r="F62" s="76"/>
+      <c r="G62" s="76"/>
       <c r="H62" s="25"/>
       <c r="I62" s="26"/>
       <c r="J62" s="72"/>
@@ -8628,39 +8632,39 @@
     <row r="65" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
       <c r="B65" s="5"/>
-      <c r="C65" s="76"/>
-      <c r="D65" s="76"/>
-      <c r="E65" s="76"/>
-      <c r="F65" s="76"/>
-      <c r="G65" s="76"/>
-      <c r="H65" s="76"/>
-      <c r="I65" s="76"/>
-      <c r="J65" s="76"/>
-      <c r="K65" s="76"/>
-      <c r="L65" s="76"/>
-      <c r="M65" s="76"/>
-      <c r="N65" s="76"/>
-      <c r="O65" s="76"/>
-      <c r="P65" s="76"/>
-      <c r="Q65" s="76"/>
-      <c r="R65" s="76"/>
-      <c r="S65" s="76"/>
-      <c r="T65" s="76"/>
-      <c r="U65" s="76"/>
-      <c r="V65" s="76"/>
-      <c r="W65" s="76"/>
-      <c r="X65" s="76"/>
-      <c r="Y65" s="76"/>
-      <c r="Z65" s="76"/>
-      <c r="AA65" s="76"/>
-      <c r="AB65" s="76"/>
-      <c r="AC65" s="76"/>
-      <c r="AD65" s="76"/>
-      <c r="AE65" s="76"/>
-      <c r="AF65" s="76"/>
-      <c r="AG65" s="76"/>
-      <c r="AH65" s="76"/>
-      <c r="AI65" s="76"/>
+      <c r="C65" s="71"/>
+      <c r="D65" s="71"/>
+      <c r="E65" s="71"/>
+      <c r="F65" s="71"/>
+      <c r="G65" s="71"/>
+      <c r="H65" s="71"/>
+      <c r="I65" s="71"/>
+      <c r="J65" s="71"/>
+      <c r="K65" s="71"/>
+      <c r="L65" s="71"/>
+      <c r="M65" s="71"/>
+      <c r="N65" s="71"/>
+      <c r="O65" s="71"/>
+      <c r="P65" s="71"/>
+      <c r="Q65" s="71"/>
+      <c r="R65" s="71"/>
+      <c r="S65" s="71"/>
+      <c r="T65" s="71"/>
+      <c r="U65" s="71"/>
+      <c r="V65" s="71"/>
+      <c r="W65" s="71"/>
+      <c r="X65" s="71"/>
+      <c r="Y65" s="71"/>
+      <c r="Z65" s="71"/>
+      <c r="AA65" s="71"/>
+      <c r="AB65" s="71"/>
+      <c r="AC65" s="71"/>
+      <c r="AD65" s="71"/>
+      <c r="AE65" s="71"/>
+      <c r="AF65" s="71"/>
+      <c r="AG65" s="71"/>
+      <c r="AH65" s="71"/>
+      <c r="AI65" s="71"/>
       <c r="AJ65" s="6"/>
       <c r="AK65" s="1"/>
       <c r="AL65" s="1"/>
@@ -8696,46 +8700,46 @@
     <row r="66" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A66" s="1"/>
       <c r="B66" s="5"/>
-      <c r="C66" s="55" t="s">
+      <c r="C66" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="D66" s="58">
+      <c r="D66" s="57">
         <f>+D27</f>
         <v>45789.8</v>
       </c>
-      <c r="E66" s="58"/>
-      <c r="F66" s="61" t="s">
+      <c r="E66" s="57"/>
+      <c r="F66" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="G66" s="61"/>
-      <c r="H66" s="61"/>
-      <c r="I66" s="61"/>
-      <c r="J66" s="61"/>
-      <c r="K66" s="61"/>
-      <c r="L66" s="61"/>
-      <c r="M66" s="61"/>
-      <c r="N66" s="61"/>
-      <c r="O66" s="61"/>
-      <c r="P66" s="61"/>
-      <c r="Q66" s="61"/>
-      <c r="R66" s="61"/>
-      <c r="S66" s="61"/>
-      <c r="T66" s="61"/>
-      <c r="U66" s="61"/>
-      <c r="V66" s="61"/>
-      <c r="W66" s="61"/>
-      <c r="X66" s="61"/>
-      <c r="Y66" s="61"/>
-      <c r="Z66" s="61"/>
-      <c r="AA66" s="61"/>
-      <c r="AB66" s="61"/>
-      <c r="AC66" s="61"/>
-      <c r="AD66" s="61"/>
-      <c r="AE66" s="61"/>
-      <c r="AF66" s="61"/>
-      <c r="AG66" s="61"/>
-      <c r="AH66" s="61"/>
-      <c r="AI66" s="61"/>
+      <c r="G66" s="60"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
+      <c r="J66" s="60"/>
+      <c r="K66" s="60"/>
+      <c r="L66" s="60"/>
+      <c r="M66" s="60"/>
+      <c r="N66" s="60"/>
+      <c r="O66" s="60"/>
+      <c r="P66" s="60"/>
+      <c r="Q66" s="60"/>
+      <c r="R66" s="60"/>
+      <c r="S66" s="60"/>
+      <c r="T66" s="60"/>
+      <c r="U66" s="60"/>
+      <c r="V66" s="60"/>
+      <c r="W66" s="60"/>
+      <c r="X66" s="60"/>
+      <c r="Y66" s="60"/>
+      <c r="Z66" s="60"/>
+      <c r="AA66" s="60"/>
+      <c r="AB66" s="60"/>
+      <c r="AC66" s="60"/>
+      <c r="AD66" s="60"/>
+      <c r="AE66" s="60"/>
+      <c r="AF66" s="60"/>
+      <c r="AG66" s="60"/>
+      <c r="AH66" s="60"/>
+      <c r="AI66" s="60"/>
       <c r="AJ66" s="6"/>
       <c r="AK66" s="1"/>
       <c r="AL66" s="1"/>
@@ -8771,39 +8775,39 @@
     <row r="67" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A67" s="1"/>
       <c r="B67" s="5"/>
-      <c r="C67" s="56"/>
-      <c r="D67" s="59"/>
-      <c r="E67" s="59"/>
-      <c r="F67" s="61"/>
-      <c r="G67" s="61"/>
-      <c r="H67" s="61"/>
-      <c r="I67" s="61"/>
-      <c r="J67" s="61"/>
-      <c r="K67" s="61"/>
-      <c r="L67" s="61"/>
-      <c r="M67" s="61"/>
-      <c r="N67" s="61"/>
-      <c r="O67" s="61"/>
-      <c r="P67" s="61"/>
-      <c r="Q67" s="61"/>
-      <c r="R67" s="61"/>
-      <c r="S67" s="61"/>
-      <c r="T67" s="61"/>
-      <c r="U67" s="61"/>
-      <c r="V67" s="61"/>
-      <c r="W67" s="61"/>
-      <c r="X67" s="61"/>
-      <c r="Y67" s="61"/>
-      <c r="Z67" s="61"/>
-      <c r="AA67" s="61"/>
-      <c r="AB67" s="61"/>
-      <c r="AC67" s="61"/>
-      <c r="AD67" s="61"/>
-      <c r="AE67" s="61"/>
-      <c r="AF67" s="61"/>
-      <c r="AG67" s="61"/>
-      <c r="AH67" s="61"/>
-      <c r="AI67" s="61"/>
+      <c r="C67" s="55"/>
+      <c r="D67" s="58"/>
+      <c r="E67" s="58"/>
+      <c r="F67" s="60"/>
+      <c r="G67" s="60"/>
+      <c r="H67" s="60"/>
+      <c r="I67" s="60"/>
+      <c r="J67" s="60"/>
+      <c r="K67" s="60"/>
+      <c r="L67" s="60"/>
+      <c r="M67" s="60"/>
+      <c r="N67" s="60"/>
+      <c r="O67" s="60"/>
+      <c r="P67" s="60"/>
+      <c r="Q67" s="60"/>
+      <c r="R67" s="60"/>
+      <c r="S67" s="60"/>
+      <c r="T67" s="60"/>
+      <c r="U67" s="60"/>
+      <c r="V67" s="60"/>
+      <c r="W67" s="60"/>
+      <c r="X67" s="60"/>
+      <c r="Y67" s="60"/>
+      <c r="Z67" s="60"/>
+      <c r="AA67" s="60"/>
+      <c r="AB67" s="60"/>
+      <c r="AC67" s="60"/>
+      <c r="AD67" s="60"/>
+      <c r="AE67" s="60"/>
+      <c r="AF67" s="60"/>
+      <c r="AG67" s="60"/>
+      <c r="AH67" s="60"/>
+      <c r="AI67" s="60"/>
       <c r="AJ67" s="6"/>
       <c r="AK67" s="1"/>
       <c r="AL67" s="1"/>
@@ -8839,41 +8843,41 @@
     <row r="68" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A68" s="1"/>
       <c r="B68" s="5"/>
-      <c r="C68" s="56"/>
-      <c r="D68" s="59"/>
-      <c r="E68" s="59"/>
-      <c r="F68" s="61" t="s">
+      <c r="C68" s="55"/>
+      <c r="D68" s="58"/>
+      <c r="E68" s="58"/>
+      <c r="F68" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="G68" s="61"/>
-      <c r="H68" s="61"/>
-      <c r="I68" s="61"/>
-      <c r="J68" s="61"/>
-      <c r="K68" s="61"/>
-      <c r="L68" s="61"/>
-      <c r="M68" s="61"/>
-      <c r="N68" s="61"/>
-      <c r="O68" s="61"/>
-      <c r="P68" s="61"/>
-      <c r="Q68" s="61"/>
-      <c r="R68" s="61"/>
-      <c r="S68" s="61"/>
-      <c r="T68" s="61"/>
-      <c r="U68" s="61"/>
-      <c r="V68" s="61"/>
-      <c r="W68" s="61"/>
-      <c r="X68" s="61"/>
-      <c r="Y68" s="61"/>
-      <c r="Z68" s="61"/>
-      <c r="AA68" s="61"/>
-      <c r="AB68" s="61"/>
-      <c r="AC68" s="61"/>
-      <c r="AD68" s="61"/>
-      <c r="AE68" s="61"/>
-      <c r="AF68" s="61"/>
-      <c r="AG68" s="61"/>
-      <c r="AH68" s="61"/>
-      <c r="AI68" s="61"/>
+      <c r="G68" s="60"/>
+      <c r="H68" s="60"/>
+      <c r="I68" s="60"/>
+      <c r="J68" s="60"/>
+      <c r="K68" s="60"/>
+      <c r="L68" s="60"/>
+      <c r="M68" s="60"/>
+      <c r="N68" s="60"/>
+      <c r="O68" s="60"/>
+      <c r="P68" s="60"/>
+      <c r="Q68" s="60"/>
+      <c r="R68" s="60"/>
+      <c r="S68" s="60"/>
+      <c r="T68" s="60"/>
+      <c r="U68" s="60"/>
+      <c r="V68" s="60"/>
+      <c r="W68" s="60"/>
+      <c r="X68" s="60"/>
+      <c r="Y68" s="60"/>
+      <c r="Z68" s="60"/>
+      <c r="AA68" s="60"/>
+      <c r="AB68" s="60"/>
+      <c r="AC68" s="60"/>
+      <c r="AD68" s="60"/>
+      <c r="AE68" s="60"/>
+      <c r="AF68" s="60"/>
+      <c r="AG68" s="60"/>
+      <c r="AH68" s="60"/>
+      <c r="AI68" s="60"/>
       <c r="AJ68" s="6"/>
       <c r="AK68" s="1"/>
       <c r="AL68" s="1"/>
@@ -8909,9 +8913,9 @@
     <row r="69" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A69" s="1"/>
       <c r="B69" s="5"/>
-      <c r="C69" s="57"/>
-      <c r="D69" s="60"/>
-      <c r="E69" s="60"/>
+      <c r="C69" s="56"/>
+      <c r="D69" s="59"/>
+      <c r="E69" s="59"/>
       <c r="F69" s="48"/>
       <c r="G69" s="48"/>
       <c r="H69" s="48"/>
@@ -8977,44 +8981,44 @@
     <row r="70" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A70" s="1"/>
       <c r="B70" s="5"/>
-      <c r="C70" s="55" t="s">
+      <c r="C70" s="54" t="s">
         <v>41</v>
       </c>
-      <c r="D70" s="58">
+      <c r="D70" s="57">
         <f>+D28</f>
         <v>45797.599999999999</v>
       </c>
-      <c r="E70" s="58"/>
-      <c r="F70" s="61"/>
-      <c r="G70" s="61"/>
-      <c r="H70" s="61"/>
-      <c r="I70" s="61"/>
-      <c r="J70" s="61"/>
-      <c r="K70" s="61"/>
-      <c r="L70" s="61"/>
-      <c r="M70" s="61"/>
-      <c r="N70" s="61"/>
-      <c r="O70" s="61"/>
-      <c r="P70" s="61"/>
-      <c r="Q70" s="61"/>
-      <c r="R70" s="61"/>
-      <c r="S70" s="61"/>
-      <c r="T70" s="61"/>
-      <c r="U70" s="61"/>
-      <c r="V70" s="61"/>
-      <c r="W70" s="61"/>
-      <c r="X70" s="61"/>
-      <c r="Y70" s="61"/>
-      <c r="Z70" s="61"/>
-      <c r="AA70" s="61"/>
-      <c r="AB70" s="61"/>
-      <c r="AC70" s="61"/>
-      <c r="AD70" s="61"/>
-      <c r="AE70" s="61"/>
-      <c r="AF70" s="61"/>
-      <c r="AG70" s="61"/>
-      <c r="AH70" s="61"/>
-      <c r="AI70" s="61"/>
+      <c r="E70" s="57"/>
+      <c r="F70" s="60"/>
+      <c r="G70" s="60"/>
+      <c r="H70" s="60"/>
+      <c r="I70" s="60"/>
+      <c r="J70" s="60"/>
+      <c r="K70" s="60"/>
+      <c r="L70" s="60"/>
+      <c r="M70" s="60"/>
+      <c r="N70" s="60"/>
+      <c r="O70" s="60"/>
+      <c r="P70" s="60"/>
+      <c r="Q70" s="60"/>
+      <c r="R70" s="60"/>
+      <c r="S70" s="60"/>
+      <c r="T70" s="60"/>
+      <c r="U70" s="60"/>
+      <c r="V70" s="60"/>
+      <c r="W70" s="60"/>
+      <c r="X70" s="60"/>
+      <c r="Y70" s="60"/>
+      <c r="Z70" s="60"/>
+      <c r="AA70" s="60"/>
+      <c r="AB70" s="60"/>
+      <c r="AC70" s="60"/>
+      <c r="AD70" s="60"/>
+      <c r="AE70" s="60"/>
+      <c r="AF70" s="60"/>
+      <c r="AG70" s="60"/>
+      <c r="AH70" s="60"/>
+      <c r="AI70" s="60"/>
       <c r="AJ70" s="6"/>
       <c r="AK70" s="1"/>
       <c r="AL70" s="1"/>
@@ -9062,41 +9066,41 @@
     <row r="71" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A71" s="1"/>
       <c r="B71" s="5"/>
-      <c r="C71" s="56"/>
-      <c r="D71" s="59"/>
-      <c r="E71" s="59"/>
-      <c r="F71" s="61" t="s">
+      <c r="C71" s="55"/>
+      <c r="D71" s="58"/>
+      <c r="E71" s="58"/>
+      <c r="F71" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="G71" s="61"/>
-      <c r="H71" s="61"/>
-      <c r="I71" s="61"/>
-      <c r="J71" s="61"/>
-      <c r="K71" s="61"/>
-      <c r="L71" s="61"/>
-      <c r="M71" s="61"/>
-      <c r="N71" s="61"/>
-      <c r="O71" s="61"/>
-      <c r="P71" s="61"/>
-      <c r="Q71" s="61"/>
-      <c r="R71" s="61"/>
-      <c r="S71" s="61"/>
-      <c r="T71" s="61"/>
-      <c r="U71" s="61"/>
-      <c r="V71" s="61"/>
-      <c r="W71" s="61"/>
-      <c r="X71" s="61"/>
-      <c r="Y71" s="61"/>
-      <c r="Z71" s="61"/>
-      <c r="AA71" s="61"/>
-      <c r="AB71" s="61"/>
-      <c r="AC71" s="61"/>
-      <c r="AD71" s="61"/>
-      <c r="AE71" s="61"/>
-      <c r="AF71" s="61"/>
-      <c r="AG71" s="61"/>
-      <c r="AH71" s="61"/>
-      <c r="AI71" s="61"/>
+      <c r="G71" s="60"/>
+      <c r="H71" s="60"/>
+      <c r="I71" s="60"/>
+      <c r="J71" s="60"/>
+      <c r="K71" s="60"/>
+      <c r="L71" s="60"/>
+      <c r="M71" s="60"/>
+      <c r="N71" s="60"/>
+      <c r="O71" s="60"/>
+      <c r="P71" s="60"/>
+      <c r="Q71" s="60"/>
+      <c r="R71" s="60"/>
+      <c r="S71" s="60"/>
+      <c r="T71" s="60"/>
+      <c r="U71" s="60"/>
+      <c r="V71" s="60"/>
+      <c r="W71" s="60"/>
+      <c r="X71" s="60"/>
+      <c r="Y71" s="60"/>
+      <c r="Z71" s="60"/>
+      <c r="AA71" s="60"/>
+      <c r="AB71" s="60"/>
+      <c r="AC71" s="60"/>
+      <c r="AD71" s="60"/>
+      <c r="AE71" s="60"/>
+      <c r="AF71" s="60"/>
+      <c r="AG71" s="60"/>
+      <c r="AH71" s="60"/>
+      <c r="AI71" s="60"/>
       <c r="AJ71" s="6"/>
       <c r="AK71" s="1"/>
       <c r="AL71" s="1"/>
@@ -9144,9 +9148,9 @@
     <row r="72" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A72" s="1"/>
       <c r="B72" s="5"/>
-      <c r="C72" s="56"/>
-      <c r="D72" s="59"/>
-      <c r="E72" s="59"/>
+      <c r="C72" s="55"/>
+      <c r="D72" s="58"/>
+      <c r="E72" s="58"/>
       <c r="F72" s="48"/>
       <c r="G72" s="48"/>
       <c r="H72" s="48"/>
@@ -9224,9 +9228,9 @@
     <row r="73" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A73" s="1"/>
       <c r="B73" s="5"/>
-      <c r="C73" s="57"/>
-      <c r="D73" s="60"/>
-      <c r="E73" s="60"/>
+      <c r="C73" s="56"/>
+      <c r="D73" s="59"/>
+      <c r="E73" s="59"/>
       <c r="F73" s="48"/>
       <c r="G73" s="48"/>
       <c r="H73" s="48"/>
@@ -9304,44 +9308,44 @@
     <row r="74" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A74" s="1"/>
       <c r="B74" s="5"/>
-      <c r="C74" s="55" t="s">
+      <c r="C74" s="54" t="s">
         <v>42</v>
       </c>
-      <c r="D74" s="58">
+      <c r="D74" s="57">
         <f>+D29</f>
         <v>45805.4</v>
       </c>
-      <c r="E74" s="58"/>
-      <c r="F74" s="61"/>
-      <c r="G74" s="61"/>
-      <c r="H74" s="61"/>
-      <c r="I74" s="61"/>
-      <c r="J74" s="61"/>
-      <c r="K74" s="61"/>
-      <c r="L74" s="61"/>
-      <c r="M74" s="61"/>
-      <c r="N74" s="61"/>
-      <c r="O74" s="61"/>
-      <c r="P74" s="61"/>
-      <c r="Q74" s="61"/>
-      <c r="R74" s="61"/>
-      <c r="S74" s="61"/>
-      <c r="T74" s="61"/>
-      <c r="U74" s="61"/>
-      <c r="V74" s="61"/>
-      <c r="W74" s="61"/>
-      <c r="X74" s="61"/>
-      <c r="Y74" s="61"/>
-      <c r="Z74" s="61"/>
-      <c r="AA74" s="61"/>
-      <c r="AB74" s="61"/>
-      <c r="AC74" s="61"/>
-      <c r="AD74" s="61"/>
-      <c r="AE74" s="61"/>
-      <c r="AF74" s="61"/>
-      <c r="AG74" s="61"/>
-      <c r="AH74" s="61"/>
-      <c r="AI74" s="61"/>
+      <c r="E74" s="57"/>
+      <c r="F74" s="60"/>
+      <c r="G74" s="60"/>
+      <c r="H74" s="60"/>
+      <c r="I74" s="60"/>
+      <c r="J74" s="60"/>
+      <c r="K74" s="60"/>
+      <c r="L74" s="60"/>
+      <c r="M74" s="60"/>
+      <c r="N74" s="60"/>
+      <c r="O74" s="60"/>
+      <c r="P74" s="60"/>
+      <c r="Q74" s="60"/>
+      <c r="R74" s="60"/>
+      <c r="S74" s="60"/>
+      <c r="T74" s="60"/>
+      <c r="U74" s="60"/>
+      <c r="V74" s="60"/>
+      <c r="W74" s="60"/>
+      <c r="X74" s="60"/>
+      <c r="Y74" s="60"/>
+      <c r="Z74" s="60"/>
+      <c r="AA74" s="60"/>
+      <c r="AB74" s="60"/>
+      <c r="AC74" s="60"/>
+      <c r="AD74" s="60"/>
+      <c r="AE74" s="60"/>
+      <c r="AF74" s="60"/>
+      <c r="AG74" s="60"/>
+      <c r="AH74" s="60"/>
+      <c r="AI74" s="60"/>
       <c r="AJ74" s="6"/>
       <c r="AK74" s="1"/>
       <c r="AL74" s="1"/>
@@ -9389,41 +9393,41 @@
     <row r="75" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A75" s="1"/>
       <c r="B75" s="5"/>
-      <c r="C75" s="56"/>
-      <c r="D75" s="59"/>
-      <c r="E75" s="59"/>
-      <c r="F75" s="61" t="s">
+      <c r="C75" s="55"/>
+      <c r="D75" s="58"/>
+      <c r="E75" s="58"/>
+      <c r="F75" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="G75" s="61"/>
-      <c r="H75" s="61"/>
-      <c r="I75" s="61"/>
-      <c r="J75" s="61"/>
-      <c r="K75" s="61"/>
-      <c r="L75" s="61"/>
-      <c r="M75" s="61"/>
-      <c r="N75" s="61"/>
-      <c r="O75" s="61"/>
-      <c r="P75" s="61"/>
-      <c r="Q75" s="61"/>
-      <c r="R75" s="61"/>
-      <c r="S75" s="61"/>
-      <c r="T75" s="61"/>
-      <c r="U75" s="61"/>
-      <c r="V75" s="61"/>
-      <c r="W75" s="61"/>
-      <c r="X75" s="61"/>
-      <c r="Y75" s="61"/>
-      <c r="Z75" s="61"/>
-      <c r="AA75" s="61"/>
-      <c r="AB75" s="61"/>
-      <c r="AC75" s="61"/>
-      <c r="AD75" s="61"/>
-      <c r="AE75" s="61"/>
-      <c r="AF75" s="61"/>
-      <c r="AG75" s="61"/>
-      <c r="AH75" s="61"/>
-      <c r="AI75" s="61"/>
+      <c r="G75" s="60"/>
+      <c r="H75" s="60"/>
+      <c r="I75" s="60"/>
+      <c r="J75" s="60"/>
+      <c r="K75" s="60"/>
+      <c r="L75" s="60"/>
+      <c r="M75" s="60"/>
+      <c r="N75" s="60"/>
+      <c r="O75" s="60"/>
+      <c r="P75" s="60"/>
+      <c r="Q75" s="60"/>
+      <c r="R75" s="60"/>
+      <c r="S75" s="60"/>
+      <c r="T75" s="60"/>
+      <c r="U75" s="60"/>
+      <c r="V75" s="60"/>
+      <c r="W75" s="60"/>
+      <c r="X75" s="60"/>
+      <c r="Y75" s="60"/>
+      <c r="Z75" s="60"/>
+      <c r="AA75" s="60"/>
+      <c r="AB75" s="60"/>
+      <c r="AC75" s="60"/>
+      <c r="AD75" s="60"/>
+      <c r="AE75" s="60"/>
+      <c r="AF75" s="60"/>
+      <c r="AG75" s="60"/>
+      <c r="AH75" s="60"/>
+      <c r="AI75" s="60"/>
       <c r="AJ75" s="6"/>
       <c r="AK75" s="1"/>
       <c r="AL75" s="1"/>
@@ -9471,9 +9475,9 @@
     <row r="76" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A76" s="1"/>
       <c r="B76" s="5"/>
-      <c r="C76" s="56"/>
-      <c r="D76" s="59"/>
-      <c r="E76" s="59"/>
+      <c r="C76" s="55"/>
+      <c r="D76" s="58"/>
+      <c r="E76" s="58"/>
       <c r="F76" s="48"/>
       <c r="G76" s="48"/>
       <c r="H76" s="48"/>
@@ -9551,9 +9555,9 @@
     <row r="77" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A77" s="1"/>
       <c r="B77" s="5"/>
-      <c r="C77" s="57"/>
-      <c r="D77" s="60"/>
-      <c r="E77" s="60"/>
+      <c r="C77" s="56"/>
+      <c r="D77" s="59"/>
+      <c r="E77" s="59"/>
       <c r="F77" s="48"/>
       <c r="G77" s="48"/>
       <c r="H77" s="48"/>
@@ -9631,44 +9635,44 @@
     <row r="78" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A78" s="1"/>
       <c r="B78" s="5"/>
-      <c r="C78" s="55" t="s">
+      <c r="C78" s="54" t="s">
         <v>43</v>
       </c>
-      <c r="D78" s="58">
+      <c r="D78" s="57">
         <f>+D30</f>
         <v>45813.2</v>
       </c>
-      <c r="E78" s="58"/>
-      <c r="F78" s="61"/>
-      <c r="G78" s="61"/>
-      <c r="H78" s="61"/>
-      <c r="I78" s="61"/>
-      <c r="J78" s="61"/>
-      <c r="K78" s="61"/>
-      <c r="L78" s="61"/>
-      <c r="M78" s="61"/>
-      <c r="N78" s="61"/>
-      <c r="O78" s="61"/>
-      <c r="P78" s="61"/>
-      <c r="Q78" s="61"/>
-      <c r="R78" s="61"/>
-      <c r="S78" s="61"/>
-      <c r="T78" s="61"/>
-      <c r="U78" s="61"/>
-      <c r="V78" s="61"/>
-      <c r="W78" s="61"/>
-      <c r="X78" s="61"/>
-      <c r="Y78" s="61"/>
-      <c r="Z78" s="61"/>
-      <c r="AA78" s="61"/>
-      <c r="AB78" s="61"/>
-      <c r="AC78" s="61"/>
-      <c r="AD78" s="61"/>
-      <c r="AE78" s="61"/>
-      <c r="AF78" s="61"/>
-      <c r="AG78" s="61"/>
-      <c r="AH78" s="61"/>
-      <c r="AI78" s="61"/>
+      <c r="E78" s="57"/>
+      <c r="F78" s="60"/>
+      <c r="G78" s="60"/>
+      <c r="H78" s="60"/>
+      <c r="I78" s="60"/>
+      <c r="J78" s="60"/>
+      <c r="K78" s="60"/>
+      <c r="L78" s="60"/>
+      <c r="M78" s="60"/>
+      <c r="N78" s="60"/>
+      <c r="O78" s="60"/>
+      <c r="P78" s="60"/>
+      <c r="Q78" s="60"/>
+      <c r="R78" s="60"/>
+      <c r="S78" s="60"/>
+      <c r="T78" s="60"/>
+      <c r="U78" s="60"/>
+      <c r="V78" s="60"/>
+      <c r="W78" s="60"/>
+      <c r="X78" s="60"/>
+      <c r="Y78" s="60"/>
+      <c r="Z78" s="60"/>
+      <c r="AA78" s="60"/>
+      <c r="AB78" s="60"/>
+      <c r="AC78" s="60"/>
+      <c r="AD78" s="60"/>
+      <c r="AE78" s="60"/>
+      <c r="AF78" s="60"/>
+      <c r="AG78" s="60"/>
+      <c r="AH78" s="60"/>
+      <c r="AI78" s="60"/>
       <c r="AJ78" s="6"/>
       <c r="AK78" s="1"/>
       <c r="AL78" s="1"/>
@@ -9716,41 +9720,41 @@
     <row r="79" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A79" s="1"/>
       <c r="B79" s="5"/>
-      <c r="C79" s="56"/>
-      <c r="D79" s="59"/>
-      <c r="E79" s="59"/>
-      <c r="F79" s="61" t="s">
+      <c r="C79" s="55"/>
+      <c r="D79" s="58"/>
+      <c r="E79" s="58"/>
+      <c r="F79" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="G79" s="61"/>
-      <c r="H79" s="61"/>
-      <c r="I79" s="61"/>
-      <c r="J79" s="61"/>
-      <c r="K79" s="61"/>
-      <c r="L79" s="61"/>
-      <c r="M79" s="61"/>
-      <c r="N79" s="61"/>
-      <c r="O79" s="61"/>
-      <c r="P79" s="61"/>
-      <c r="Q79" s="61"/>
-      <c r="R79" s="61"/>
-      <c r="S79" s="61"/>
-      <c r="T79" s="61"/>
-      <c r="U79" s="61"/>
-      <c r="V79" s="61"/>
-      <c r="W79" s="61"/>
-      <c r="X79" s="61"/>
-      <c r="Y79" s="61"/>
-      <c r="Z79" s="61"/>
-      <c r="AA79" s="61"/>
-      <c r="AB79" s="61"/>
-      <c r="AC79" s="61"/>
-      <c r="AD79" s="61"/>
-      <c r="AE79" s="61"/>
-      <c r="AF79" s="61"/>
-      <c r="AG79" s="61"/>
-      <c r="AH79" s="61"/>
-      <c r="AI79" s="61"/>
+      <c r="G79" s="60"/>
+      <c r="H79" s="60"/>
+      <c r="I79" s="60"/>
+      <c r="J79" s="60"/>
+      <c r="K79" s="60"/>
+      <c r="L79" s="60"/>
+      <c r="M79" s="60"/>
+      <c r="N79" s="60"/>
+      <c r="O79" s="60"/>
+      <c r="P79" s="60"/>
+      <c r="Q79" s="60"/>
+      <c r="R79" s="60"/>
+      <c r="S79" s="60"/>
+      <c r="T79" s="60"/>
+      <c r="U79" s="60"/>
+      <c r="V79" s="60"/>
+      <c r="W79" s="60"/>
+      <c r="X79" s="60"/>
+      <c r="Y79" s="60"/>
+      <c r="Z79" s="60"/>
+      <c r="AA79" s="60"/>
+      <c r="AB79" s="60"/>
+      <c r="AC79" s="60"/>
+      <c r="AD79" s="60"/>
+      <c r="AE79" s="60"/>
+      <c r="AF79" s="60"/>
+      <c r="AG79" s="60"/>
+      <c r="AH79" s="60"/>
+      <c r="AI79" s="60"/>
       <c r="AJ79" s="6"/>
       <c r="AK79" s="1"/>
       <c r="AL79" s="1"/>
@@ -9798,9 +9802,9 @@
     <row r="80" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A80" s="1"/>
       <c r="B80" s="5"/>
-      <c r="C80" s="56"/>
-      <c r="D80" s="59"/>
-      <c r="E80" s="59"/>
+      <c r="C80" s="55"/>
+      <c r="D80" s="58"/>
+      <c r="E80" s="58"/>
       <c r="F80" s="48"/>
       <c r="G80" s="48"/>
       <c r="H80" s="48"/>
@@ -9878,9 +9882,9 @@
     <row r="81" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A81" s="1"/>
       <c r="B81" s="5"/>
-      <c r="C81" s="57"/>
-      <c r="D81" s="60"/>
-      <c r="E81" s="60"/>
+      <c r="C81" s="56"/>
+      <c r="D81" s="59"/>
+      <c r="E81" s="59"/>
       <c r="F81" s="48"/>
       <c r="G81" s="48"/>
       <c r="H81" s="48"/>
@@ -9958,44 +9962,44 @@
     <row r="82" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A82" s="1"/>
       <c r="B82" s="5"/>
-      <c r="C82" s="55" t="s">
+      <c r="C82" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="D82" s="58">
+      <c r="D82" s="57">
         <f>+D31</f>
         <v>45821</v>
       </c>
-      <c r="E82" s="58"/>
-      <c r="F82" s="61"/>
-      <c r="G82" s="61"/>
-      <c r="H82" s="61"/>
-      <c r="I82" s="61"/>
-      <c r="J82" s="61"/>
-      <c r="K82" s="61"/>
-      <c r="L82" s="61"/>
-      <c r="M82" s="61"/>
-      <c r="N82" s="61"/>
-      <c r="O82" s="61"/>
-      <c r="P82" s="61"/>
-      <c r="Q82" s="61"/>
-      <c r="R82" s="61"/>
-      <c r="S82" s="61"/>
-      <c r="T82" s="61"/>
-      <c r="U82" s="61"/>
-      <c r="V82" s="61"/>
-      <c r="W82" s="61"/>
-      <c r="X82" s="61"/>
-      <c r="Y82" s="61"/>
-      <c r="Z82" s="61"/>
-      <c r="AA82" s="61"/>
-      <c r="AB82" s="61"/>
-      <c r="AC82" s="61"/>
-      <c r="AD82" s="61"/>
-      <c r="AE82" s="61"/>
-      <c r="AF82" s="61"/>
-      <c r="AG82" s="61"/>
-      <c r="AH82" s="61"/>
-      <c r="AI82" s="61"/>
+      <c r="E82" s="57"/>
+      <c r="F82" s="60"/>
+      <c r="G82" s="60"/>
+      <c r="H82" s="60"/>
+      <c r="I82" s="60"/>
+      <c r="J82" s="60"/>
+      <c r="K82" s="60"/>
+      <c r="L82" s="60"/>
+      <c r="M82" s="60"/>
+      <c r="N82" s="60"/>
+      <c r="O82" s="60"/>
+      <c r="P82" s="60"/>
+      <c r="Q82" s="60"/>
+      <c r="R82" s="60"/>
+      <c r="S82" s="60"/>
+      <c r="T82" s="60"/>
+      <c r="U82" s="60"/>
+      <c r="V82" s="60"/>
+      <c r="W82" s="60"/>
+      <c r="X82" s="60"/>
+      <c r="Y82" s="60"/>
+      <c r="Z82" s="60"/>
+      <c r="AA82" s="60"/>
+      <c r="AB82" s="60"/>
+      <c r="AC82" s="60"/>
+      <c r="AD82" s="60"/>
+      <c r="AE82" s="60"/>
+      <c r="AF82" s="60"/>
+      <c r="AG82" s="60"/>
+      <c r="AH82" s="60"/>
+      <c r="AI82" s="60"/>
       <c r="AJ82" s="6"/>
       <c r="AK82" s="1"/>
       <c r="AL82" s="1"/>
@@ -10043,41 +10047,41 @@
     <row r="83" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A83" s="1"/>
       <c r="B83" s="5"/>
-      <c r="C83" s="56"/>
-      <c r="D83" s="59"/>
-      <c r="E83" s="59"/>
-      <c r="F83" s="61" t="s">
+      <c r="C83" s="55"/>
+      <c r="D83" s="58"/>
+      <c r="E83" s="58"/>
+      <c r="F83" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="G83" s="61"/>
-      <c r="H83" s="61"/>
-      <c r="I83" s="61"/>
-      <c r="J83" s="61"/>
-      <c r="K83" s="61"/>
-      <c r="L83" s="61"/>
-      <c r="M83" s="61"/>
-      <c r="N83" s="61"/>
-      <c r="O83" s="61"/>
-      <c r="P83" s="61"/>
-      <c r="Q83" s="61"/>
-      <c r="R83" s="61"/>
-      <c r="S83" s="61"/>
-      <c r="T83" s="61"/>
-      <c r="U83" s="61"/>
-      <c r="V83" s="61"/>
-      <c r="W83" s="61"/>
-      <c r="X83" s="61"/>
-      <c r="Y83" s="61"/>
-      <c r="Z83" s="61"/>
-      <c r="AA83" s="61"/>
-      <c r="AB83" s="61"/>
-      <c r="AC83" s="61"/>
-      <c r="AD83" s="61"/>
-      <c r="AE83" s="61"/>
-      <c r="AF83" s="61"/>
-      <c r="AG83" s="61"/>
-      <c r="AH83" s="61"/>
-      <c r="AI83" s="61"/>
+      <c r="G83" s="60"/>
+      <c r="H83" s="60"/>
+      <c r="I83" s="60"/>
+      <c r="J83" s="60"/>
+      <c r="K83" s="60"/>
+      <c r="L83" s="60"/>
+      <c r="M83" s="60"/>
+      <c r="N83" s="60"/>
+      <c r="O83" s="60"/>
+      <c r="P83" s="60"/>
+      <c r="Q83" s="60"/>
+      <c r="R83" s="60"/>
+      <c r="S83" s="60"/>
+      <c r="T83" s="60"/>
+      <c r="U83" s="60"/>
+      <c r="V83" s="60"/>
+      <c r="W83" s="60"/>
+      <c r="X83" s="60"/>
+      <c r="Y83" s="60"/>
+      <c r="Z83" s="60"/>
+      <c r="AA83" s="60"/>
+      <c r="AB83" s="60"/>
+      <c r="AC83" s="60"/>
+      <c r="AD83" s="60"/>
+      <c r="AE83" s="60"/>
+      <c r="AF83" s="60"/>
+      <c r="AG83" s="60"/>
+      <c r="AH83" s="60"/>
+      <c r="AI83" s="60"/>
       <c r="AJ83" s="6"/>
       <c r="AK83" s="1"/>
       <c r="AL83" s="1"/>
@@ -10125,9 +10129,9 @@
     <row r="84" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A84" s="1"/>
       <c r="B84" s="5"/>
-      <c r="C84" s="56"/>
-      <c r="D84" s="59"/>
-      <c r="E84" s="59"/>
+      <c r="C84" s="55"/>
+      <c r="D84" s="58"/>
+      <c r="E84" s="58"/>
       <c r="F84" s="48"/>
       <c r="G84" s="48"/>
       <c r="H84" s="48"/>
@@ -10205,9 +10209,9 @@
     <row r="85" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A85" s="1"/>
       <c r="B85" s="5"/>
-      <c r="C85" s="57"/>
-      <c r="D85" s="60"/>
-      <c r="E85" s="60"/>
+      <c r="C85" s="56"/>
+      <c r="D85" s="59"/>
+      <c r="E85" s="59"/>
       <c r="F85" s="48"/>
       <c r="G85" s="48"/>
       <c r="H85" s="48"/>
@@ -10285,44 +10289,44 @@
     <row r="86" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A86" s="1"/>
       <c r="B86" s="5"/>
-      <c r="C86" s="55" t="s">
+      <c r="C86" s="54" t="s">
         <v>45</v>
       </c>
-      <c r="D86" s="58">
+      <c r="D86" s="57">
         <f>+D32</f>
         <v>45828.800000000003</v>
       </c>
-      <c r="E86" s="58"/>
-      <c r="F86" s="61"/>
-      <c r="G86" s="61"/>
-      <c r="H86" s="61"/>
-      <c r="I86" s="61"/>
-      <c r="J86" s="61"/>
-      <c r="K86" s="61"/>
-      <c r="L86" s="61"/>
-      <c r="M86" s="61"/>
-      <c r="N86" s="61"/>
-      <c r="O86" s="61"/>
-      <c r="P86" s="61"/>
-      <c r="Q86" s="61"/>
-      <c r="R86" s="61"/>
-      <c r="S86" s="61"/>
-      <c r="T86" s="61"/>
-      <c r="U86" s="61"/>
-      <c r="V86" s="61"/>
-      <c r="W86" s="61"/>
-      <c r="X86" s="61"/>
-      <c r="Y86" s="61"/>
-      <c r="Z86" s="61"/>
-      <c r="AA86" s="61"/>
-      <c r="AB86" s="61"/>
-      <c r="AC86" s="61"/>
-      <c r="AD86" s="61"/>
-      <c r="AE86" s="61"/>
-      <c r="AF86" s="61"/>
-      <c r="AG86" s="61"/>
-      <c r="AH86" s="61"/>
-      <c r="AI86" s="61"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="60"/>
+      <c r="G86" s="60"/>
+      <c r="H86" s="60"/>
+      <c r="I86" s="60"/>
+      <c r="J86" s="60"/>
+      <c r="K86" s="60"/>
+      <c r="L86" s="60"/>
+      <c r="M86" s="60"/>
+      <c r="N86" s="60"/>
+      <c r="O86" s="60"/>
+      <c r="P86" s="60"/>
+      <c r="Q86" s="60"/>
+      <c r="R86" s="60"/>
+      <c r="S86" s="60"/>
+      <c r="T86" s="60"/>
+      <c r="U86" s="60"/>
+      <c r="V86" s="60"/>
+      <c r="W86" s="60"/>
+      <c r="X86" s="60"/>
+      <c r="Y86" s="60"/>
+      <c r="Z86" s="60"/>
+      <c r="AA86" s="60"/>
+      <c r="AB86" s="60"/>
+      <c r="AC86" s="60"/>
+      <c r="AD86" s="60"/>
+      <c r="AE86" s="60"/>
+      <c r="AF86" s="60"/>
+      <c r="AG86" s="60"/>
+      <c r="AH86" s="60"/>
+      <c r="AI86" s="60"/>
       <c r="AJ86" s="6"/>
       <c r="AK86" s="1"/>
       <c r="AL86" s="1"/>
@@ -10370,41 +10374,41 @@
     <row r="87" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A87" s="1"/>
       <c r="B87" s="5"/>
-      <c r="C87" s="56"/>
-      <c r="D87" s="59"/>
-      <c r="E87" s="59"/>
-      <c r="F87" s="71" t="s">
+      <c r="C87" s="55"/>
+      <c r="D87" s="58"/>
+      <c r="E87" s="58"/>
+      <c r="F87" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="G87" s="61"/>
-      <c r="H87" s="61"/>
-      <c r="I87" s="61"/>
-      <c r="J87" s="61"/>
-      <c r="K87" s="61"/>
-      <c r="L87" s="61"/>
-      <c r="M87" s="61"/>
-      <c r="N87" s="61"/>
-      <c r="O87" s="61"/>
-      <c r="P87" s="61"/>
-      <c r="Q87" s="61"/>
-      <c r="R87" s="61"/>
-      <c r="S87" s="61"/>
-      <c r="T87" s="61"/>
-      <c r="U87" s="61"/>
-      <c r="V87" s="61"/>
-      <c r="W87" s="61"/>
-      <c r="X87" s="61"/>
-      <c r="Y87" s="61"/>
-      <c r="Z87" s="61"/>
-      <c r="AA87" s="61"/>
-      <c r="AB87" s="61"/>
-      <c r="AC87" s="61"/>
-      <c r="AD87" s="61"/>
-      <c r="AE87" s="61"/>
-      <c r="AF87" s="61"/>
-      <c r="AG87" s="61"/>
-      <c r="AH87" s="61"/>
-      <c r="AI87" s="61"/>
+      <c r="G87" s="60"/>
+      <c r="H87" s="60"/>
+      <c r="I87" s="60"/>
+      <c r="J87" s="60"/>
+      <c r="K87" s="60"/>
+      <c r="L87" s="60"/>
+      <c r="M87" s="60"/>
+      <c r="N87" s="60"/>
+      <c r="O87" s="60"/>
+      <c r="P87" s="60"/>
+      <c r="Q87" s="60"/>
+      <c r="R87" s="60"/>
+      <c r="S87" s="60"/>
+      <c r="T87" s="60"/>
+      <c r="U87" s="60"/>
+      <c r="V87" s="60"/>
+      <c r="W87" s="60"/>
+      <c r="X87" s="60"/>
+      <c r="Y87" s="60"/>
+      <c r="Z87" s="60"/>
+      <c r="AA87" s="60"/>
+      <c r="AB87" s="60"/>
+      <c r="AC87" s="60"/>
+      <c r="AD87" s="60"/>
+      <c r="AE87" s="60"/>
+      <c r="AF87" s="60"/>
+      <c r="AG87" s="60"/>
+      <c r="AH87" s="60"/>
+      <c r="AI87" s="60"/>
       <c r="AJ87" s="6"/>
       <c r="AK87" s="1"/>
       <c r="AL87" s="1"/>
@@ -10452,9 +10456,9 @@
     <row r="88" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A88" s="1"/>
       <c r="B88" s="5"/>
-      <c r="C88" s="56"/>
-      <c r="D88" s="59"/>
-      <c r="E88" s="59"/>
+      <c r="C88" s="55"/>
+      <c r="D88" s="58"/>
+      <c r="E88" s="58"/>
       <c r="F88" s="48"/>
       <c r="G88" s="48"/>
       <c r="H88" s="48"/>
@@ -10532,9 +10536,9 @@
     <row r="89" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A89" s="1"/>
       <c r="B89" s="5"/>
-      <c r="C89" s="57"/>
-      <c r="D89" s="60"/>
-      <c r="E89" s="60"/>
+      <c r="C89" s="56"/>
+      <c r="D89" s="59"/>
+      <c r="E89" s="59"/>
       <c r="F89" s="48"/>
       <c r="G89" s="48"/>
       <c r="H89" s="48"/>
@@ -10612,44 +10616,44 @@
     <row r="90" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A90" s="1"/>
       <c r="B90" s="5"/>
-      <c r="C90" s="55" t="s">
+      <c r="C90" s="54" t="s">
         <v>46</v>
       </c>
-      <c r="D90" s="58">
+      <c r="D90" s="57">
         <f>+D33</f>
         <v>45836.6</v>
       </c>
-      <c r="E90" s="58"/>
-      <c r="F90" s="61"/>
-      <c r="G90" s="61"/>
-      <c r="H90" s="61"/>
-      <c r="I90" s="61"/>
-      <c r="J90" s="61"/>
-      <c r="K90" s="61"/>
-      <c r="L90" s="61"/>
-      <c r="M90" s="61"/>
-      <c r="N90" s="61"/>
-      <c r="O90" s="61"/>
-      <c r="P90" s="61"/>
-      <c r="Q90" s="61"/>
-      <c r="R90" s="61"/>
-      <c r="S90" s="61"/>
-      <c r="T90" s="61"/>
-      <c r="U90" s="61"/>
-      <c r="V90" s="61"/>
-      <c r="W90" s="61"/>
-      <c r="X90" s="61"/>
-      <c r="Y90" s="61"/>
-      <c r="Z90" s="61"/>
-      <c r="AA90" s="61"/>
-      <c r="AB90" s="61"/>
-      <c r="AC90" s="61"/>
-      <c r="AD90" s="61"/>
-      <c r="AE90" s="61"/>
-      <c r="AF90" s="61"/>
-      <c r="AG90" s="61"/>
-      <c r="AH90" s="61"/>
-      <c r="AI90" s="61"/>
+      <c r="E90" s="57"/>
+      <c r="F90" s="60"/>
+      <c r="G90" s="60"/>
+      <c r="H90" s="60"/>
+      <c r="I90" s="60"/>
+      <c r="J90" s="60"/>
+      <c r="K90" s="60"/>
+      <c r="L90" s="60"/>
+      <c r="M90" s="60"/>
+      <c r="N90" s="60"/>
+      <c r="O90" s="60"/>
+      <c r="P90" s="60"/>
+      <c r="Q90" s="60"/>
+      <c r="R90" s="60"/>
+      <c r="S90" s="60"/>
+      <c r="T90" s="60"/>
+      <c r="U90" s="60"/>
+      <c r="V90" s="60"/>
+      <c r="W90" s="60"/>
+      <c r="X90" s="60"/>
+      <c r="Y90" s="60"/>
+      <c r="Z90" s="60"/>
+      <c r="AA90" s="60"/>
+      <c r="AB90" s="60"/>
+      <c r="AC90" s="60"/>
+      <c r="AD90" s="60"/>
+      <c r="AE90" s="60"/>
+      <c r="AF90" s="60"/>
+      <c r="AG90" s="60"/>
+      <c r="AH90" s="60"/>
+      <c r="AI90" s="60"/>
       <c r="AJ90" s="6"/>
       <c r="AK90" s="1"/>
       <c r="AL90" s="1"/>
@@ -10697,41 +10701,41 @@
     <row r="91" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A91" s="1"/>
       <c r="B91" s="5"/>
-      <c r="C91" s="56"/>
-      <c r="D91" s="59"/>
-      <c r="E91" s="59"/>
-      <c r="F91" s="71" t="s">
+      <c r="C91" s="55"/>
+      <c r="D91" s="58"/>
+      <c r="E91" s="58"/>
+      <c r="F91" s="61" t="s">
         <v>71</v>
       </c>
-      <c r="G91" s="61"/>
-      <c r="H91" s="61"/>
-      <c r="I91" s="61"/>
-      <c r="J91" s="61"/>
-      <c r="K91" s="61"/>
-      <c r="L91" s="61"/>
-      <c r="M91" s="61"/>
-      <c r="N91" s="61"/>
-      <c r="O91" s="61"/>
-      <c r="P91" s="61"/>
-      <c r="Q91" s="61"/>
-      <c r="R91" s="61"/>
-      <c r="S91" s="61"/>
-      <c r="T91" s="61"/>
-      <c r="U91" s="61"/>
-      <c r="V91" s="61"/>
-      <c r="W91" s="61"/>
-      <c r="X91" s="61"/>
-      <c r="Y91" s="61"/>
-      <c r="Z91" s="61"/>
-      <c r="AA91" s="61"/>
-      <c r="AB91" s="61"/>
-      <c r="AC91" s="61"/>
-      <c r="AD91" s="61"/>
-      <c r="AE91" s="61"/>
-      <c r="AF91" s="61"/>
-      <c r="AG91" s="61"/>
-      <c r="AH91" s="61"/>
-      <c r="AI91" s="61"/>
+      <c r="G91" s="60"/>
+      <c r="H91" s="60"/>
+      <c r="I91" s="60"/>
+      <c r="J91" s="60"/>
+      <c r="K91" s="60"/>
+      <c r="L91" s="60"/>
+      <c r="M91" s="60"/>
+      <c r="N91" s="60"/>
+      <c r="O91" s="60"/>
+      <c r="P91" s="60"/>
+      <c r="Q91" s="60"/>
+      <c r="R91" s="60"/>
+      <c r="S91" s="60"/>
+      <c r="T91" s="60"/>
+      <c r="U91" s="60"/>
+      <c r="V91" s="60"/>
+      <c r="W91" s="60"/>
+      <c r="X91" s="60"/>
+      <c r="Y91" s="60"/>
+      <c r="Z91" s="60"/>
+      <c r="AA91" s="60"/>
+      <c r="AB91" s="60"/>
+      <c r="AC91" s="60"/>
+      <c r="AD91" s="60"/>
+      <c r="AE91" s="60"/>
+      <c r="AF91" s="60"/>
+      <c r="AG91" s="60"/>
+      <c r="AH91" s="60"/>
+      <c r="AI91" s="60"/>
       <c r="AJ91" s="6"/>
       <c r="AK91" s="1"/>
       <c r="AL91" s="1"/>
@@ -10779,9 +10783,9 @@
     <row r="92" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A92" s="1"/>
       <c r="B92" s="5"/>
-      <c r="C92" s="56"/>
-      <c r="D92" s="59"/>
-      <c r="E92" s="59"/>
+      <c r="C92" s="55"/>
+      <c r="D92" s="58"/>
+      <c r="E92" s="58"/>
       <c r="F92" s="48"/>
       <c r="G92" s="48"/>
       <c r="H92" s="48"/>
@@ -10859,9 +10863,9 @@
     <row r="93" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A93" s="1"/>
       <c r="B93" s="5"/>
-      <c r="C93" s="57"/>
-      <c r="D93" s="60"/>
-      <c r="E93" s="60"/>
+      <c r="C93" s="56"/>
+      <c r="D93" s="59"/>
+      <c r="E93" s="59"/>
       <c r="F93" s="48"/>
       <c r="G93" s="48"/>
       <c r="H93" s="48"/>
@@ -10939,44 +10943,44 @@
     <row r="94" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A94" s="1"/>
       <c r="B94" s="5"/>
-      <c r="C94" s="55" t="s">
+      <c r="C94" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="D94" s="58">
+      <c r="D94" s="57">
         <f>+D34</f>
         <v>45844.4</v>
       </c>
-      <c r="E94" s="58"/>
-      <c r="F94" s="61"/>
-      <c r="G94" s="61"/>
-      <c r="H94" s="61"/>
-      <c r="I94" s="61"/>
-      <c r="J94" s="61"/>
-      <c r="K94" s="61"/>
-      <c r="L94" s="61"/>
-      <c r="M94" s="61"/>
-      <c r="N94" s="61"/>
-      <c r="O94" s="61"/>
-      <c r="P94" s="61"/>
-      <c r="Q94" s="61"/>
-      <c r="R94" s="61"/>
-      <c r="S94" s="61"/>
-      <c r="T94" s="61"/>
-      <c r="U94" s="61"/>
-      <c r="V94" s="61"/>
-      <c r="W94" s="61"/>
-      <c r="X94" s="61"/>
-      <c r="Y94" s="61"/>
-      <c r="Z94" s="61"/>
-      <c r="AA94" s="61"/>
-      <c r="AB94" s="61"/>
-      <c r="AC94" s="61"/>
-      <c r="AD94" s="61"/>
-      <c r="AE94" s="61"/>
-      <c r="AF94" s="61"/>
-      <c r="AG94" s="61"/>
-      <c r="AH94" s="61"/>
-      <c r="AI94" s="61"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="60"/>
+      <c r="G94" s="60"/>
+      <c r="H94" s="60"/>
+      <c r="I94" s="60"/>
+      <c r="J94" s="60"/>
+      <c r="K94" s="60"/>
+      <c r="L94" s="60"/>
+      <c r="M94" s="60"/>
+      <c r="N94" s="60"/>
+      <c r="O94" s="60"/>
+      <c r="P94" s="60"/>
+      <c r="Q94" s="60"/>
+      <c r="R94" s="60"/>
+      <c r="S94" s="60"/>
+      <c r="T94" s="60"/>
+      <c r="U94" s="60"/>
+      <c r="V94" s="60"/>
+      <c r="W94" s="60"/>
+      <c r="X94" s="60"/>
+      <c r="Y94" s="60"/>
+      <c r="Z94" s="60"/>
+      <c r="AA94" s="60"/>
+      <c r="AB94" s="60"/>
+      <c r="AC94" s="60"/>
+      <c r="AD94" s="60"/>
+      <c r="AE94" s="60"/>
+      <c r="AF94" s="60"/>
+      <c r="AG94" s="60"/>
+      <c r="AH94" s="60"/>
+      <c r="AI94" s="60"/>
       <c r="AJ94" s="6"/>
       <c r="AK94" s="1"/>
       <c r="AL94" s="1"/>
@@ -11024,41 +11028,41 @@
     <row r="95" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A95" s="1"/>
       <c r="B95" s="5"/>
-      <c r="C95" s="56"/>
-      <c r="D95" s="59"/>
-      <c r="E95" s="59"/>
-      <c r="F95" s="71" t="s">
+      <c r="C95" s="55"/>
+      <c r="D95" s="58"/>
+      <c r="E95" s="58"/>
+      <c r="F95" s="61" t="s">
         <v>72</v>
       </c>
-      <c r="G95" s="61"/>
-      <c r="H95" s="61"/>
-      <c r="I95" s="61"/>
-      <c r="J95" s="61"/>
-      <c r="K95" s="61"/>
-      <c r="L95" s="61"/>
-      <c r="M95" s="61"/>
-      <c r="N95" s="61"/>
-      <c r="O95" s="61"/>
-      <c r="P95" s="61"/>
-      <c r="Q95" s="61"/>
-      <c r="R95" s="61"/>
-      <c r="S95" s="61"/>
-      <c r="T95" s="61"/>
-      <c r="U95" s="61"/>
-      <c r="V95" s="61"/>
-      <c r="W95" s="61"/>
-      <c r="X95" s="61"/>
-      <c r="Y95" s="61"/>
-      <c r="Z95" s="61"/>
-      <c r="AA95" s="61"/>
-      <c r="AB95" s="61"/>
-      <c r="AC95" s="61"/>
-      <c r="AD95" s="61"/>
-      <c r="AE95" s="61"/>
-      <c r="AF95" s="61"/>
-      <c r="AG95" s="61"/>
-      <c r="AH95" s="61"/>
-      <c r="AI95" s="61"/>
+      <c r="G95" s="60"/>
+      <c r="H95" s="60"/>
+      <c r="I95" s="60"/>
+      <c r="J95" s="60"/>
+      <c r="K95" s="60"/>
+      <c r="L95" s="60"/>
+      <c r="M95" s="60"/>
+      <c r="N95" s="60"/>
+      <c r="O95" s="60"/>
+      <c r="P95" s="60"/>
+      <c r="Q95" s="60"/>
+      <c r="R95" s="60"/>
+      <c r="S95" s="60"/>
+      <c r="T95" s="60"/>
+      <c r="U95" s="60"/>
+      <c r="V95" s="60"/>
+      <c r="W95" s="60"/>
+      <c r="X95" s="60"/>
+      <c r="Y95" s="60"/>
+      <c r="Z95" s="60"/>
+      <c r="AA95" s="60"/>
+      <c r="AB95" s="60"/>
+      <c r="AC95" s="60"/>
+      <c r="AD95" s="60"/>
+      <c r="AE95" s="60"/>
+      <c r="AF95" s="60"/>
+      <c r="AG95" s="60"/>
+      <c r="AH95" s="60"/>
+      <c r="AI95" s="60"/>
       <c r="AJ95" s="6"/>
       <c r="AK95" s="1"/>
       <c r="AL95" s="1"/>
@@ -11106,9 +11110,9 @@
     <row r="96" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A96" s="1"/>
       <c r="B96" s="5"/>
-      <c r="C96" s="56"/>
-      <c r="D96" s="59"/>
-      <c r="E96" s="59"/>
+      <c r="C96" s="55"/>
+      <c r="D96" s="58"/>
+      <c r="E96" s="58"/>
       <c r="F96" s="48"/>
       <c r="G96" s="48"/>
       <c r="H96" s="48"/>
@@ -11186,9 +11190,9 @@
     <row r="97" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A97" s="1"/>
       <c r="B97" s="5"/>
-      <c r="C97" s="57"/>
-      <c r="D97" s="60"/>
-      <c r="E97" s="60"/>
+      <c r="C97" s="56"/>
+      <c r="D97" s="59"/>
+      <c r="E97" s="59"/>
       <c r="F97" s="48"/>
       <c r="G97" s="48"/>
       <c r="H97" s="48"/>
@@ -11266,44 +11270,44 @@
     <row r="98" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A98" s="1"/>
       <c r="B98" s="5"/>
-      <c r="C98" s="55" t="s">
+      <c r="C98" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="D98" s="58">
+      <c r="D98" s="57">
         <f>+D35</f>
         <v>45852.2</v>
       </c>
-      <c r="E98" s="58"/>
-      <c r="F98" s="61"/>
-      <c r="G98" s="61"/>
-      <c r="H98" s="61"/>
-      <c r="I98" s="61"/>
-      <c r="J98" s="61"/>
-      <c r="K98" s="61"/>
-      <c r="L98" s="61"/>
-      <c r="M98" s="61"/>
-      <c r="N98" s="61"/>
-      <c r="O98" s="61"/>
-      <c r="P98" s="61"/>
-      <c r="Q98" s="61"/>
-      <c r="R98" s="61"/>
-      <c r="S98" s="61"/>
-      <c r="T98" s="61"/>
-      <c r="U98" s="61"/>
-      <c r="V98" s="61"/>
-      <c r="W98" s="61"/>
-      <c r="X98" s="61"/>
-      <c r="Y98" s="61"/>
-      <c r="Z98" s="61"/>
-      <c r="AA98" s="61"/>
-      <c r="AB98" s="61"/>
-      <c r="AC98" s="61"/>
-      <c r="AD98" s="61"/>
-      <c r="AE98" s="61"/>
-      <c r="AF98" s="61"/>
-      <c r="AG98" s="61"/>
-      <c r="AH98" s="61"/>
-      <c r="AI98" s="61"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="60"/>
+      <c r="G98" s="60"/>
+      <c r="H98" s="60"/>
+      <c r="I98" s="60"/>
+      <c r="J98" s="60"/>
+      <c r="K98" s="60"/>
+      <c r="L98" s="60"/>
+      <c r="M98" s="60"/>
+      <c r="N98" s="60"/>
+      <c r="O98" s="60"/>
+      <c r="P98" s="60"/>
+      <c r="Q98" s="60"/>
+      <c r="R98" s="60"/>
+      <c r="S98" s="60"/>
+      <c r="T98" s="60"/>
+      <c r="U98" s="60"/>
+      <c r="V98" s="60"/>
+      <c r="W98" s="60"/>
+      <c r="X98" s="60"/>
+      <c r="Y98" s="60"/>
+      <c r="Z98" s="60"/>
+      <c r="AA98" s="60"/>
+      <c r="AB98" s="60"/>
+      <c r="AC98" s="60"/>
+      <c r="AD98" s="60"/>
+      <c r="AE98" s="60"/>
+      <c r="AF98" s="60"/>
+      <c r="AG98" s="60"/>
+      <c r="AH98" s="60"/>
+      <c r="AI98" s="60"/>
       <c r="AJ98" s="6"/>
       <c r="AK98" s="1"/>
       <c r="AL98" s="1"/>
@@ -11351,41 +11355,41 @@
     <row r="99" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A99" s="1"/>
       <c r="B99" s="5"/>
-      <c r="C99" s="56"/>
-      <c r="D99" s="59"/>
-      <c r="E99" s="59"/>
-      <c r="F99" s="61" t="s">
+      <c r="C99" s="55"/>
+      <c r="D99" s="58"/>
+      <c r="E99" s="58"/>
+      <c r="F99" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="G99" s="61"/>
-      <c r="H99" s="61"/>
-      <c r="I99" s="61"/>
-      <c r="J99" s="61"/>
-      <c r="K99" s="61"/>
-      <c r="L99" s="61"/>
-      <c r="M99" s="61"/>
-      <c r="N99" s="61"/>
-      <c r="O99" s="61"/>
-      <c r="P99" s="61"/>
-      <c r="Q99" s="61"/>
-      <c r="R99" s="61"/>
-      <c r="S99" s="61"/>
-      <c r="T99" s="61"/>
-      <c r="U99" s="61"/>
-      <c r="V99" s="61"/>
-      <c r="W99" s="61"/>
-      <c r="X99" s="61"/>
-      <c r="Y99" s="61"/>
-      <c r="Z99" s="61"/>
-      <c r="AA99" s="61"/>
-      <c r="AB99" s="61"/>
-      <c r="AC99" s="61"/>
-      <c r="AD99" s="61"/>
-      <c r="AE99" s="61"/>
-      <c r="AF99" s="61"/>
-      <c r="AG99" s="61"/>
-      <c r="AH99" s="61"/>
-      <c r="AI99" s="61"/>
+      <c r="G99" s="60"/>
+      <c r="H99" s="60"/>
+      <c r="I99" s="60"/>
+      <c r="J99" s="60"/>
+      <c r="K99" s="60"/>
+      <c r="L99" s="60"/>
+      <c r="M99" s="60"/>
+      <c r="N99" s="60"/>
+      <c r="O99" s="60"/>
+      <c r="P99" s="60"/>
+      <c r="Q99" s="60"/>
+      <c r="R99" s="60"/>
+      <c r="S99" s="60"/>
+      <c r="T99" s="60"/>
+      <c r="U99" s="60"/>
+      <c r="V99" s="60"/>
+      <c r="W99" s="60"/>
+      <c r="X99" s="60"/>
+      <c r="Y99" s="60"/>
+      <c r="Z99" s="60"/>
+      <c r="AA99" s="60"/>
+      <c r="AB99" s="60"/>
+      <c r="AC99" s="60"/>
+      <c r="AD99" s="60"/>
+      <c r="AE99" s="60"/>
+      <c r="AF99" s="60"/>
+      <c r="AG99" s="60"/>
+      <c r="AH99" s="60"/>
+      <c r="AI99" s="60"/>
       <c r="AJ99" s="6"/>
       <c r="AK99" s="1"/>
       <c r="AL99" s="1"/>
@@ -11433,9 +11437,9 @@
     <row r="100" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A100" s="1"/>
       <c r="B100" s="5"/>
-      <c r="C100" s="56"/>
-      <c r="D100" s="59"/>
-      <c r="E100" s="59"/>
+      <c r="C100" s="55"/>
+      <c r="D100" s="58"/>
+      <c r="E100" s="58"/>
       <c r="F100" s="48"/>
       <c r="G100" s="48"/>
       <c r="H100" s="48"/>
@@ -11513,9 +11517,9 @@
     <row r="101" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A101" s="1"/>
       <c r="B101" s="5"/>
-      <c r="C101" s="57"/>
-      <c r="D101" s="60"/>
-      <c r="E101" s="60"/>
+      <c r="C101" s="56"/>
+      <c r="D101" s="59"/>
+      <c r="E101" s="59"/>
       <c r="F101" s="48"/>
       <c r="G101" s="48"/>
       <c r="H101" s="48"/>
@@ -11593,44 +11597,44 @@
     <row r="102" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A102" s="1"/>
       <c r="B102" s="5"/>
-      <c r="C102" s="55" t="s">
+      <c r="C102" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="D102" s="58">
+      <c r="D102" s="57">
         <f>+D36</f>
         <v>45860</v>
       </c>
-      <c r="E102" s="58"/>
-      <c r="F102" s="61"/>
-      <c r="G102" s="61"/>
-      <c r="H102" s="61"/>
-      <c r="I102" s="61"/>
-      <c r="J102" s="61"/>
-      <c r="K102" s="61"/>
-      <c r="L102" s="61"/>
-      <c r="M102" s="61"/>
-      <c r="N102" s="61"/>
-      <c r="O102" s="61"/>
-      <c r="P102" s="61"/>
-      <c r="Q102" s="61"/>
-      <c r="R102" s="61"/>
-      <c r="S102" s="61"/>
-      <c r="T102" s="61"/>
-      <c r="U102" s="61"/>
-      <c r="V102" s="61"/>
-      <c r="W102" s="61"/>
-      <c r="X102" s="61"/>
-      <c r="Y102" s="61"/>
-      <c r="Z102" s="61"/>
-      <c r="AA102" s="61"/>
-      <c r="AB102" s="61"/>
-      <c r="AC102" s="61"/>
-      <c r="AD102" s="61"/>
-      <c r="AE102" s="61"/>
-      <c r="AF102" s="61"/>
-      <c r="AG102" s="61"/>
-      <c r="AH102" s="61"/>
-      <c r="AI102" s="61"/>
+      <c r="E102" s="57"/>
+      <c r="F102" s="60"/>
+      <c r="G102" s="60"/>
+      <c r="H102" s="60"/>
+      <c r="I102" s="60"/>
+      <c r="J102" s="60"/>
+      <c r="K102" s="60"/>
+      <c r="L102" s="60"/>
+      <c r="M102" s="60"/>
+      <c r="N102" s="60"/>
+      <c r="O102" s="60"/>
+      <c r="P102" s="60"/>
+      <c r="Q102" s="60"/>
+      <c r="R102" s="60"/>
+      <c r="S102" s="60"/>
+      <c r="T102" s="60"/>
+      <c r="U102" s="60"/>
+      <c r="V102" s="60"/>
+      <c r="W102" s="60"/>
+      <c r="X102" s="60"/>
+      <c r="Y102" s="60"/>
+      <c r="Z102" s="60"/>
+      <c r="AA102" s="60"/>
+      <c r="AB102" s="60"/>
+      <c r="AC102" s="60"/>
+      <c r="AD102" s="60"/>
+      <c r="AE102" s="60"/>
+      <c r="AF102" s="60"/>
+      <c r="AG102" s="60"/>
+      <c r="AH102" s="60"/>
+      <c r="AI102" s="60"/>
       <c r="AJ102" s="6"/>
       <c r="AK102" s="1"/>
       <c r="AL102" s="1"/>
@@ -11678,41 +11682,41 @@
     <row r="103" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A103" s="1"/>
       <c r="B103" s="5"/>
-      <c r="C103" s="56"/>
-      <c r="D103" s="59"/>
-      <c r="E103" s="59"/>
-      <c r="F103" s="61" t="s">
+      <c r="C103" s="55"/>
+      <c r="D103" s="58"/>
+      <c r="E103" s="58"/>
+      <c r="F103" s="60" t="s">
         <v>74</v>
       </c>
-      <c r="G103" s="61"/>
-      <c r="H103" s="61"/>
-      <c r="I103" s="61"/>
-      <c r="J103" s="61"/>
-      <c r="K103" s="61"/>
-      <c r="L103" s="61"/>
-      <c r="M103" s="61"/>
-      <c r="N103" s="61"/>
-      <c r="O103" s="61"/>
-      <c r="P103" s="61"/>
-      <c r="Q103" s="61"/>
-      <c r="R103" s="61"/>
-      <c r="S103" s="61"/>
-      <c r="T103" s="61"/>
-      <c r="U103" s="61"/>
-      <c r="V103" s="61"/>
-      <c r="W103" s="61"/>
-      <c r="X103" s="61"/>
-      <c r="Y103" s="61"/>
-      <c r="Z103" s="61"/>
-      <c r="AA103" s="61"/>
-      <c r="AB103" s="61"/>
-      <c r="AC103" s="61"/>
-      <c r="AD103" s="61"/>
-      <c r="AE103" s="61"/>
-      <c r="AF103" s="61"/>
-      <c r="AG103" s="61"/>
-      <c r="AH103" s="61"/>
-      <c r="AI103" s="61"/>
+      <c r="G103" s="60"/>
+      <c r="H103" s="60"/>
+      <c r="I103" s="60"/>
+      <c r="J103" s="60"/>
+      <c r="K103" s="60"/>
+      <c r="L103" s="60"/>
+      <c r="M103" s="60"/>
+      <c r="N103" s="60"/>
+      <c r="O103" s="60"/>
+      <c r="P103" s="60"/>
+      <c r="Q103" s="60"/>
+      <c r="R103" s="60"/>
+      <c r="S103" s="60"/>
+      <c r="T103" s="60"/>
+      <c r="U103" s="60"/>
+      <c r="V103" s="60"/>
+      <c r="W103" s="60"/>
+      <c r="X103" s="60"/>
+      <c r="Y103" s="60"/>
+      <c r="Z103" s="60"/>
+      <c r="AA103" s="60"/>
+      <c r="AB103" s="60"/>
+      <c r="AC103" s="60"/>
+      <c r="AD103" s="60"/>
+      <c r="AE103" s="60"/>
+      <c r="AF103" s="60"/>
+      <c r="AG103" s="60"/>
+      <c r="AH103" s="60"/>
+      <c r="AI103" s="60"/>
       <c r="AJ103" s="6"/>
       <c r="AK103" s="1"/>
       <c r="AL103" s="1"/>
@@ -11760,9 +11764,9 @@
     <row r="104" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A104" s="1"/>
       <c r="B104" s="5"/>
-      <c r="C104" s="56"/>
-      <c r="D104" s="59"/>
-      <c r="E104" s="59"/>
+      <c r="C104" s="55"/>
+      <c r="D104" s="58"/>
+      <c r="E104" s="58"/>
       <c r="F104" s="48"/>
       <c r="G104" s="48"/>
       <c r="H104" s="48"/>
@@ -11840,9 +11844,9 @@
     <row r="105" spans="1:78" x14ac:dyDescent="0.3">
       <c r="A105" s="1"/>
       <c r="B105" s="5"/>
-      <c r="C105" s="57"/>
-      <c r="D105" s="60"/>
-      <c r="E105" s="60"/>
+      <c r="C105" s="56"/>
+      <c r="D105" s="59"/>
+      <c r="E105" s="59"/>
       <c r="F105" s="48"/>
       <c r="G105" s="48"/>
       <c r="H105" s="48"/>
@@ -13441,7 +13445,7 @@
       <c r="BY124" s="8"/>
       <c r="BZ124" s="8"/>
     </row>
-    <row r="125" spans="1:78" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:78" ht="44.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -19650,6 +19654,11 @@
     <mergeCell ref="R42:S42"/>
     <mergeCell ref="AF42:AG42"/>
     <mergeCell ref="AH42:AI42"/>
+    <mergeCell ref="V42:W42"/>
+    <mergeCell ref="X42:Y42"/>
+    <mergeCell ref="Z42:AA42"/>
+    <mergeCell ref="AB42:AC42"/>
+    <mergeCell ref="AD42:AE42"/>
     <mergeCell ref="C43:C45"/>
     <mergeCell ref="E43:G43"/>
     <mergeCell ref="J43:K43"/>
@@ -19659,11 +19668,11 @@
     <mergeCell ref="R43:S43"/>
     <mergeCell ref="T43:U43"/>
     <mergeCell ref="T42:U42"/>
-    <mergeCell ref="V42:W42"/>
-    <mergeCell ref="X42:Y42"/>
-    <mergeCell ref="Z42:AA42"/>
-    <mergeCell ref="AB42:AC42"/>
-    <mergeCell ref="AD42:AE42"/>
+    <mergeCell ref="E45:G45"/>
+    <mergeCell ref="J45:K45"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="P45:Q45"/>
     <mergeCell ref="AH43:AI43"/>
     <mergeCell ref="E44:G44"/>
     <mergeCell ref="J44:K44"/>
@@ -19685,11 +19694,8 @@
     <mergeCell ref="AD44:AE44"/>
     <mergeCell ref="AF44:AG44"/>
     <mergeCell ref="AH44:AI44"/>
-    <mergeCell ref="E45:G45"/>
-    <mergeCell ref="J45:K45"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="P45:Q45"/>
+    <mergeCell ref="T46:U46"/>
+    <mergeCell ref="V46:W46"/>
     <mergeCell ref="AD45:AE45"/>
     <mergeCell ref="AF45:AG45"/>
     <mergeCell ref="AH45:AI45"/>
@@ -19712,8 +19718,14 @@
     <mergeCell ref="AD47:AE47"/>
     <mergeCell ref="AF47:AG47"/>
     <mergeCell ref="AH47:AI47"/>
-    <mergeCell ref="AF46:AG46"/>
-    <mergeCell ref="AH46:AI46"/>
+    <mergeCell ref="V48:W48"/>
+    <mergeCell ref="X48:Y48"/>
+    <mergeCell ref="Z48:AA48"/>
+    <mergeCell ref="AB48:AC48"/>
+    <mergeCell ref="E48:G48"/>
+    <mergeCell ref="J48:K48"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="N48:O48"/>
     <mergeCell ref="E47:G47"/>
     <mergeCell ref="J47:K47"/>
     <mergeCell ref="L47:M47"/>
@@ -19722,15 +19734,6 @@
     <mergeCell ref="R47:S47"/>
     <mergeCell ref="T47:U47"/>
     <mergeCell ref="V47:W47"/>
-    <mergeCell ref="T46:U46"/>
-    <mergeCell ref="V46:W46"/>
-    <mergeCell ref="X46:Y46"/>
-    <mergeCell ref="Z46:AA46"/>
-    <mergeCell ref="AB46:AC46"/>
-    <mergeCell ref="AD46:AE46"/>
-    <mergeCell ref="AD48:AE48"/>
-    <mergeCell ref="AF48:AG48"/>
-    <mergeCell ref="AH48:AI48"/>
     <mergeCell ref="E49:G49"/>
     <mergeCell ref="J49:K49"/>
     <mergeCell ref="L49:M49"/>
@@ -19740,14 +19743,21 @@
     <mergeCell ref="T49:U49"/>
     <mergeCell ref="R48:S48"/>
     <mergeCell ref="T48:U48"/>
-    <mergeCell ref="V48:W48"/>
-    <mergeCell ref="X48:Y48"/>
-    <mergeCell ref="Z48:AA48"/>
-    <mergeCell ref="AB48:AC48"/>
-    <mergeCell ref="E48:G48"/>
-    <mergeCell ref="J48:K48"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="N48:O48"/>
+    <mergeCell ref="AF50:AG50"/>
+    <mergeCell ref="AH50:AI50"/>
+    <mergeCell ref="X46:Y46"/>
+    <mergeCell ref="Z46:AA46"/>
+    <mergeCell ref="AB46:AC46"/>
+    <mergeCell ref="AD46:AE46"/>
+    <mergeCell ref="AD48:AE48"/>
+    <mergeCell ref="AF48:AG48"/>
+    <mergeCell ref="AH48:AI48"/>
+    <mergeCell ref="AF46:AG46"/>
+    <mergeCell ref="AH46:AI46"/>
+    <mergeCell ref="C48:C50"/>
+    <mergeCell ref="AB51:AC51"/>
+    <mergeCell ref="AD51:AE51"/>
+    <mergeCell ref="AF51:AG51"/>
     <mergeCell ref="P48:Q48"/>
     <mergeCell ref="AH49:AI49"/>
     <mergeCell ref="E50:G50"/>
@@ -19768,17 +19778,6 @@
     <mergeCell ref="Z50:AA50"/>
     <mergeCell ref="AB50:AC50"/>
     <mergeCell ref="AD50:AE50"/>
-    <mergeCell ref="AF50:AG50"/>
-    <mergeCell ref="AH50:AI50"/>
-    <mergeCell ref="C51:C52"/>
-    <mergeCell ref="E51:G51"/>
-    <mergeCell ref="J51:K51"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="AB51:AC51"/>
-    <mergeCell ref="AD51:AE51"/>
-    <mergeCell ref="AF51:AG51"/>
     <mergeCell ref="AH51:AI51"/>
     <mergeCell ref="E52:G52"/>
     <mergeCell ref="J52:K52"/>
@@ -19794,6 +19793,15 @@
     <mergeCell ref="Z51:AA51"/>
     <mergeCell ref="AF52:AG52"/>
     <mergeCell ref="AH52:AI52"/>
+    <mergeCell ref="V52:W52"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="Z52:AA52"/>
+    <mergeCell ref="AB52:AC52"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="E51:G51"/>
+    <mergeCell ref="J51:K51"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="N51:O51"/>
     <mergeCell ref="C53:C55"/>
     <mergeCell ref="E53:G53"/>
     <mergeCell ref="J53:K53"/>
@@ -19803,11 +19811,12 @@
     <mergeCell ref="R53:S53"/>
     <mergeCell ref="T53:U53"/>
     <mergeCell ref="T52:U52"/>
-    <mergeCell ref="V52:W52"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="Z52:AA52"/>
-    <mergeCell ref="AB52:AC52"/>
-    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="J55:K55"/>
+    <mergeCell ref="L55:M55"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="P55:Q55"/>
+    <mergeCell ref="C51:C52"/>
     <mergeCell ref="AH53:AI53"/>
     <mergeCell ref="E54:G54"/>
     <mergeCell ref="J54:K54"/>
@@ -19829,11 +19838,6 @@
     <mergeCell ref="AD54:AE54"/>
     <mergeCell ref="AF54:AG54"/>
     <mergeCell ref="AH54:AI54"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="J55:K55"/>
-    <mergeCell ref="L55:M55"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="P55:Q55"/>
     <mergeCell ref="AD55:AE55"/>
     <mergeCell ref="AF55:AG55"/>
     <mergeCell ref="AH55:AI55"/>
@@ -19892,7 +19896,6 @@
     <mergeCell ref="J58:K58"/>
     <mergeCell ref="L58:M58"/>
     <mergeCell ref="N58:O58"/>
-    <mergeCell ref="P58:Q58"/>
     <mergeCell ref="AH59:AI59"/>
     <mergeCell ref="E60:G60"/>
     <mergeCell ref="J60:K60"/>
@@ -19923,6 +19926,13 @@
     <mergeCell ref="AB61:AC61"/>
     <mergeCell ref="AD61:AE61"/>
     <mergeCell ref="AF61:AG61"/>
+    <mergeCell ref="P58:Q58"/>
+    <mergeCell ref="T62:U62"/>
+    <mergeCell ref="V62:W62"/>
+    <mergeCell ref="X62:Y62"/>
+    <mergeCell ref="Z62:AA62"/>
+    <mergeCell ref="AB62:AC62"/>
+    <mergeCell ref="AD62:AE62"/>
     <mergeCell ref="AH61:AI61"/>
     <mergeCell ref="E62:G62"/>
     <mergeCell ref="J62:K62"/>
@@ -19938,25 +19948,6 @@
     <mergeCell ref="Z61:AA61"/>
     <mergeCell ref="AF62:AG62"/>
     <mergeCell ref="AH62:AI62"/>
-    <mergeCell ref="C65:AI65"/>
-    <mergeCell ref="C66:C69"/>
-    <mergeCell ref="D66:E69"/>
-    <mergeCell ref="F66:AI66"/>
-    <mergeCell ref="F67:AI67"/>
-    <mergeCell ref="F68:AI68"/>
-    <mergeCell ref="T62:U62"/>
-    <mergeCell ref="V62:W62"/>
-    <mergeCell ref="X62:Y62"/>
-    <mergeCell ref="Z62:AA62"/>
-    <mergeCell ref="AB62:AC62"/>
-    <mergeCell ref="AD62:AE62"/>
-    <mergeCell ref="D78:E81"/>
-    <mergeCell ref="F78:AI78"/>
-    <mergeCell ref="F79:AI79"/>
-    <mergeCell ref="C82:C85"/>
-    <mergeCell ref="D82:E85"/>
-    <mergeCell ref="F82:AI82"/>
-    <mergeCell ref="F83:AI83"/>
     <mergeCell ref="C70:C73"/>
     <mergeCell ref="D70:E73"/>
     <mergeCell ref="F70:AI70"/>
@@ -19965,6 +19956,12 @@
     <mergeCell ref="D74:E77"/>
     <mergeCell ref="F74:AI74"/>
     <mergeCell ref="F75:AI75"/>
+    <mergeCell ref="C65:AI65"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="D66:E69"/>
+    <mergeCell ref="F66:AI66"/>
+    <mergeCell ref="F67:AI67"/>
+    <mergeCell ref="F68:AI68"/>
     <mergeCell ref="C102:C105"/>
     <mergeCell ref="D102:E105"/>
     <mergeCell ref="F102:AI102"/>
@@ -19987,6 +19984,13 @@
     <mergeCell ref="F90:AI90"/>
     <mergeCell ref="F91:AI91"/>
     <mergeCell ref="C78:C81"/>
+    <mergeCell ref="D78:E81"/>
+    <mergeCell ref="F78:AI78"/>
+    <mergeCell ref="F79:AI79"/>
+    <mergeCell ref="C82:C85"/>
+    <mergeCell ref="D82:E85"/>
+    <mergeCell ref="F82:AI82"/>
+    <mergeCell ref="F83:AI83"/>
   </mergeCells>
   <conditionalFormatting sqref="C42:C43 C53 C58 G63">
     <cfRule type="expression" dxfId="1" priority="2">
@@ -19999,32 +20003,12 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="145" scale="29" fitToWidth="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="29" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="4beaf995-bca9-4e52-9e7c-0ff6540365ad" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="38982260-ffbb-4d45-bf74-3f340fef217a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008179FB738B52054CB49D1EA14F3B017D" ma:contentTypeVersion="11" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="5cf92993d4be1ca8d869739abdcab03f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="38982260-ffbb-4d45-bf74-3f340fef217a" xmlns:ns3="4beaf995-bca9-4e52-9e7c-0ff6540365ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="306cbce10ee737f78145650a7152b8c6" ns2:_="" ns3:_="">
     <xsd:import namespace="38982260-ffbb-4d45-bf74-3f340fef217a"/>
@@ -20219,26 +20203,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63AA2A11-AE46-4A5F-BCE6-D7C99ABA7B52}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="4beaf995-bca9-4e52-9e7c-0ff6540365ad"/>
-    <ds:schemaRef ds:uri="38982260-ffbb-4d45-bf74-3f340fef217a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="4beaf995-bca9-4e52-9e7c-0ff6540365ad" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="38982260-ffbb-4d45-bf74-3f340fef217a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2FF41B7-BE2E-48D2-BC55-8A6E9BC4A2FF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4C091D35-AD75-4799-8EE0-19856AF47B28}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -20255,4 +20240,23 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63AA2A11-AE46-4A5F-BCE6-D7C99ABA7B52}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4beaf995-bca9-4e52-9e7c-0ff6540365ad"/>
+    <ds:schemaRef ds:uri="38982260-ffbb-4d45-bf74-3f340fef217a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A2FF41B7-BE2E-48D2-BC55-8A6E9BC4A2FF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>